--- a/data_lake/bart_temp_med/dt=2026-07-28/temperaturamed.xlsx
+++ b/data_lake/bart_temp_med/dt=2026-07-28/temperaturamed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\01. Tematicas\05. Datos Hidrometeorologicos\01. Productos\02.Tablas\temporales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD13D070-F907-4FDD-9AA2-7E74070833DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5B64C2-3E4E-40AF-9265-CE2F16615416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="729" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6354,8 +6354,8 @@
     <col min="43" max="43" width="20.7109375" style="53" customWidth="1"/>
     <col min="44" max="44" width="24.85546875" style="69" customWidth="1"/>
     <col min="45" max="45" width="13.28515625" style="70" bestFit="1" customWidth="1"/>
-    <col min="46" max="113" width="32.42578125" style="50" customWidth="1"/>
-    <col min="114" max="16384" width="32.42578125" style="50"/>
+    <col min="46" max="114" width="32.42578125" style="50" customWidth="1"/>
+    <col min="115" max="16384" width="32.42578125" style="50"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.2">
@@ -6716,18 +6716,20 @@
       <c r="AJ5" s="56">
         <v>29.5</v>
       </c>
-      <c r="AK5" s="56"/>
+      <c r="AK5" s="56">
+        <v>29.1</v>
+      </c>
       <c r="AL5" s="56"/>
       <c r="AM5" s="56"/>
       <c r="AN5" s="56"/>
       <c r="AO5" s="56"/>
       <c r="AP5" s="58">
         <f t="shared" ref="AP5:AP68" si="0">COUNTIF(K5:AO5,"&gt;0")</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ5" s="71">
         <f t="shared" ref="AQ5:AQ68" si="1">IF(AP5&gt;14,AVERAGE(K5:AO5),"")</f>
-        <v>28.830769230769228</v>
+        <v>28.840740740740738</v>
       </c>
       <c r="AR5" s="71">
         <f>IFERROR(VLOOKUP(A5,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -6735,7 +6737,7 @@
       </c>
       <c r="AS5" s="71">
         <f t="shared" ref="AS5:AS68" si="2">IF(OR(AQ5="",AR5=""),"",IFERROR(AQ5-AR5,""))</f>
-        <v>0.6775543417979577</v>
+        <v>0.68752585176946823</v>
       </c>
     </row>
     <row r="6" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6847,18 +6849,20 @@
       <c r="AJ6" s="56">
         <v>29.1</v>
       </c>
-      <c r="AK6" s="56"/>
+      <c r="AK6" s="56">
+        <v>29.1</v>
+      </c>
       <c r="AL6" s="56"/>
       <c r="AM6" s="56"/>
       <c r="AN6" s="56"/>
       <c r="AO6" s="56"/>
       <c r="AP6" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ6" s="71">
         <f t="shared" si="1"/>
-        <v>28.842307692307692</v>
+        <v>28.851851851851851</v>
       </c>
       <c r="AR6" s="71">
         <f>IFERROR(VLOOKUP(A6,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -6866,7 +6870,7 @@
       </c>
       <c r="AS6" s="71">
         <f t="shared" si="2"/>
-        <v>0.44707380335887237</v>
+        <v>0.45661796290303158</v>
       </c>
     </row>
     <row r="7" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6978,18 +6982,20 @@
       <c r="AJ7" s="56">
         <v>31.5</v>
       </c>
-      <c r="AK7" s="56"/>
+      <c r="AK7" s="56">
+        <v>30.5</v>
+      </c>
       <c r="AL7" s="56"/>
       <c r="AM7" s="56"/>
       <c r="AN7" s="56"/>
       <c r="AO7" s="56"/>
       <c r="AP7" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ7" s="71">
         <f t="shared" si="1"/>
-        <v>31.446153846153848</v>
+        <v>31.411111111111111</v>
       </c>
       <c r="AR7" s="71">
         <f>IFERROR(VLOOKUP(A7,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -6997,7 +7003,7 @@
       </c>
       <c r="AS7" s="71">
         <f t="shared" si="2"/>
-        <v>2.2459733546023877</v>
+        <v>2.210930619559651</v>
       </c>
     </row>
     <row r="8" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7109,18 +7115,20 @@
       <c r="AJ8" s="56">
         <v>29.4</v>
       </c>
-      <c r="AK8" s="56"/>
+      <c r="AK8" s="56">
+        <v>28.7</v>
+      </c>
       <c r="AL8" s="56"/>
       <c r="AM8" s="56"/>
       <c r="AN8" s="56"/>
       <c r="AO8" s="56"/>
       <c r="AP8" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ8" s="71">
         <f t="shared" si="1"/>
-        <v>29.700000000000003</v>
+        <v>29.662962962962965</v>
       </c>
       <c r="AR8" s="71">
         <f>IFERROR(VLOOKUP(A8,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7128,7 +7136,7 @@
       </c>
       <c r="AS8" s="71">
         <f t="shared" si="2"/>
-        <v>1.1214606838286016</v>
+        <v>1.0844236467915636</v>
       </c>
     </row>
     <row r="9" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7240,18 +7248,20 @@
       <c r="AJ9" s="56">
         <v>28.9</v>
       </c>
-      <c r="AK9" s="56"/>
+      <c r="AK9" s="56">
+        <v>28.1</v>
+      </c>
       <c r="AL9" s="56"/>
       <c r="AM9" s="56"/>
       <c r="AN9" s="56"/>
       <c r="AO9" s="56"/>
       <c r="AP9" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ9" s="71">
         <f t="shared" si="1"/>
-        <v>29.36538461538462</v>
+        <v>29.318518518518523</v>
       </c>
       <c r="AR9" s="71">
         <f>IFERROR(VLOOKUP(A9,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7259,7 +7269,7 @@
       </c>
       <c r="AS9" s="71">
         <f t="shared" si="2"/>
-        <v>-0.42208436724560983</v>
+        <v>-0.46895046411170682</v>
       </c>
     </row>
     <row r="10" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7371,18 +7381,20 @@
       <c r="AJ10" s="56">
         <v>31.4</v>
       </c>
-      <c r="AK10" s="56"/>
+      <c r="AK10" s="56">
+        <v>29.3</v>
+      </c>
       <c r="AL10" s="56"/>
       <c r="AM10" s="56"/>
       <c r="AN10" s="56"/>
       <c r="AO10" s="56"/>
       <c r="AP10" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ10" s="71">
         <f t="shared" si="1"/>
-        <v>31.673076923076923</v>
+        <v>31.585185185185182</v>
       </c>
       <c r="AR10" s="71">
         <f>IFERROR(VLOOKUP(A10,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7390,7 +7402,7 @@
       </c>
       <c r="AS10" s="71">
         <f t="shared" si="2"/>
-        <v>1.593654888671864</v>
+        <v>1.5057631507801226</v>
       </c>
     </row>
     <row r="11" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7502,18 +7514,20 @@
       <c r="AJ11" s="56">
         <v>30.9</v>
       </c>
-      <c r="AK11" s="56"/>
+      <c r="AK11" s="56">
+        <v>31.1</v>
+      </c>
       <c r="AL11" s="56"/>
       <c r="AM11" s="56"/>
       <c r="AN11" s="56"/>
       <c r="AO11" s="56"/>
       <c r="AP11" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ11" s="71">
         <f t="shared" si="1"/>
-        <v>32.58461538461539</v>
+        <v>32.529629629629632</v>
       </c>
       <c r="AR11" s="71">
         <f>IFERROR(VLOOKUP(A11,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7521,7 +7535,7 @@
       </c>
       <c r="AS11" s="71">
         <f t="shared" si="2"/>
-        <v>2.5807013073875389</v>
+        <v>2.5257155524017811</v>
       </c>
     </row>
     <row r="12" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7633,18 +7647,20 @@
       <c r="AJ12" s="56">
         <v>28.3</v>
       </c>
-      <c r="AK12" s="56"/>
+      <c r="AK12" s="56">
+        <v>28.3</v>
+      </c>
       <c r="AL12" s="56"/>
       <c r="AM12" s="56"/>
       <c r="AN12" s="56"/>
       <c r="AO12" s="56"/>
       <c r="AP12" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ12" s="71">
         <f t="shared" si="1"/>
-        <v>30.046153846153839</v>
+        <v>29.981481481481474</v>
       </c>
       <c r="AR12" s="71">
         <f>IFERROR(VLOOKUP(A12,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7652,7 +7668,7 @@
       </c>
       <c r="AS12" s="71">
         <f t="shared" si="2"/>
-        <v>1.7804874568382587</v>
+        <v>1.7158150921658937</v>
       </c>
     </row>
     <row r="13" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7764,18 +7780,20 @@
       <c r="AJ13" s="56">
         <v>29.1</v>
       </c>
-      <c r="AK13" s="56"/>
+      <c r="AK13" s="56">
+        <v>29.3</v>
+      </c>
       <c r="AL13" s="56"/>
       <c r="AM13" s="56"/>
       <c r="AN13" s="56"/>
       <c r="AO13" s="56"/>
       <c r="AP13" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ13" s="71">
         <f t="shared" si="1"/>
-        <v>29.919230769230765</v>
+        <v>29.896296296296288</v>
       </c>
       <c r="AR13" s="71">
         <f>IFERROR(VLOOKUP(A13,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7783,7 +7801,7 @@
       </c>
       <c r="AS13" s="71">
         <f t="shared" si="2"/>
-        <v>1.5898360714184037</v>
+        <v>1.566901598483927</v>
       </c>
     </row>
     <row r="14" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7895,18 +7913,20 @@
       <c r="AJ14" s="56">
         <v>23.6</v>
       </c>
-      <c r="AK14" s="56"/>
+      <c r="AK14" s="56">
+        <v>23.2</v>
+      </c>
       <c r="AL14" s="56"/>
       <c r="AM14" s="56"/>
       <c r="AN14" s="56"/>
       <c r="AO14" s="56"/>
       <c r="AP14" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ14" s="71">
         <f t="shared" si="1"/>
-        <v>23.599999999999998</v>
+        <v>23.585185185185182</v>
       </c>
       <c r="AR14" s="71">
         <f>IFERROR(VLOOKUP(A14,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7914,7 +7934,7 @@
       </c>
       <c r="AS14" s="71">
         <f t="shared" si="2"/>
-        <v>1.8784599761051481</v>
+        <v>1.8636451612903322</v>
       </c>
     </row>
     <row r="15" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8026,18 +8046,20 @@
       <c r="AJ15" s="56">
         <v>29.9</v>
       </c>
-      <c r="AK15" s="56"/>
+      <c r="AK15" s="56">
+        <v>29</v>
+      </c>
       <c r="AL15" s="56"/>
       <c r="AM15" s="56"/>
       <c r="AN15" s="56"/>
       <c r="AO15" s="56"/>
       <c r="AP15" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ15" s="71">
         <f t="shared" si="1"/>
-        <v>29.188461538461539</v>
+        <v>29.18148148148148</v>
       </c>
       <c r="AR15" s="71">
         <f>IFERROR(VLOOKUP(A15,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8045,7 +8067,7 @@
       </c>
       <c r="AS15" s="71">
         <f t="shared" si="2"/>
-        <v>0.95295616211745937</v>
+        <v>0.94597610513740094</v>
       </c>
     </row>
     <row r="16" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8157,18 +8179,20 @@
       <c r="AJ16" s="56">
         <v>27.3</v>
       </c>
-      <c r="AK16" s="56"/>
+      <c r="AK16" s="56">
+        <v>28.7</v>
+      </c>
       <c r="AL16" s="56"/>
       <c r="AM16" s="56"/>
       <c r="AN16" s="56"/>
       <c r="AO16" s="56"/>
       <c r="AP16" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ16" s="71">
         <f t="shared" si="1"/>
-        <v>28.346153846153847</v>
+        <v>28.359259259259261</v>
       </c>
       <c r="AR16" s="71">
         <f>IFERROR(VLOOKUP(A16,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8176,7 +8200,7 @@
       </c>
       <c r="AS16" s="71">
         <f t="shared" si="2"/>
-        <v>0.70850099775086761</v>
+        <v>0.72160641085628185</v>
       </c>
     </row>
     <row r="17" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8288,18 +8312,20 @@
       <c r="AJ17" s="56">
         <v>23.1</v>
       </c>
-      <c r="AK17" s="56"/>
+      <c r="AK17" s="56">
+        <v>23.6</v>
+      </c>
       <c r="AL17" s="56"/>
       <c r="AM17" s="56"/>
       <c r="AN17" s="56"/>
       <c r="AO17" s="56"/>
       <c r="AP17" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ17" s="71">
         <f t="shared" si="1"/>
-        <v>24.630769230769236</v>
+        <v>24.592592592592595</v>
       </c>
       <c r="AR17" s="71">
         <f>IFERROR(VLOOKUP(A17,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8307,7 +8333,7 @@
       </c>
       <c r="AS17" s="71">
         <f t="shared" si="2"/>
-        <v>0.64714556161303705</v>
+        <v>0.60896892343639664</v>
       </c>
     </row>
     <row r="18" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8419,18 +8445,20 @@
       <c r="AJ18" s="56">
         <v>18.7</v>
       </c>
-      <c r="AK18" s="56"/>
+      <c r="AK18" s="56">
+        <v>18.399999999999999</v>
+      </c>
       <c r="AL18" s="56"/>
       <c r="AM18" s="56"/>
       <c r="AN18" s="56"/>
       <c r="AO18" s="56"/>
       <c r="AP18" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ18" s="71">
         <f t="shared" si="1"/>
-        <v>18.765384615384615</v>
+        <v>18.751851851851853</v>
       </c>
       <c r="AR18" s="71">
         <f>IFERROR(VLOOKUP(A18,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8438,7 +8466,7 @@
       </c>
       <c r="AS18" s="71">
         <f t="shared" si="2"/>
-        <v>1.3470333609043337</v>
+        <v>1.3335005973715717</v>
       </c>
     </row>
     <row r="19" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8550,18 +8578,20 @@
       <c r="AJ19" s="56">
         <v>23</v>
       </c>
-      <c r="AK19" s="56"/>
+      <c r="AK19" s="56">
+        <v>23</v>
+      </c>
       <c r="AL19" s="56"/>
       <c r="AM19" s="56"/>
       <c r="AN19" s="56"/>
       <c r="AO19" s="56"/>
       <c r="AP19" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ19" s="71">
         <f t="shared" si="1"/>
-        <v>24.226923076923075</v>
+        <v>24.18148148148148</v>
       </c>
       <c r="AR19" s="71">
         <f>IFERROR(VLOOKUP(A19,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8569,7 +8599,7 @@
       </c>
       <c r="AS19" s="71">
         <f t="shared" si="2"/>
-        <v>2.0933881306865239</v>
+        <v>2.0479465352449289</v>
       </c>
     </row>
     <row r="20" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8681,18 +8711,20 @@
       <c r="AJ20" s="56">
         <v>23.6</v>
       </c>
-      <c r="AK20" s="56"/>
+      <c r="AK20" s="56">
+        <v>23.8</v>
+      </c>
       <c r="AL20" s="56"/>
       <c r="AM20" s="56"/>
       <c r="AN20" s="56"/>
       <c r="AO20" s="56"/>
       <c r="AP20" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ20" s="71">
         <f t="shared" si="1"/>
-        <v>24.257692307692306</v>
+        <v>24.240740740740737</v>
       </c>
       <c r="AR20" s="71">
         <f>IFERROR(VLOOKUP(A20,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8700,7 +8732,7 @@
       </c>
       <c r="AS20" s="71">
         <f t="shared" si="2"/>
-        <v>1.6500268817204358</v>
+        <v>1.6330753147688668</v>
       </c>
     </row>
     <row r="21" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8812,18 +8844,20 @@
       <c r="AJ21" s="56">
         <v>27</v>
       </c>
-      <c r="AK21" s="56"/>
+      <c r="AK21" s="56">
+        <v>27.1</v>
+      </c>
       <c r="AL21" s="56"/>
       <c r="AM21" s="56"/>
       <c r="AN21" s="56"/>
       <c r="AO21" s="56"/>
       <c r="AP21" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ21" s="71">
         <f t="shared" si="1"/>
-        <v>27.123076923076919</v>
+        <v>27.12222222222222</v>
       </c>
       <c r="AR21" s="71">
         <f>IFERROR(VLOOKUP(A21,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8831,7 +8865,7 @@
       </c>
       <c r="AS21" s="71">
         <f t="shared" si="2"/>
-        <v>2.4329950313197877</v>
+        <v>2.4321403304650886</v>
       </c>
     </row>
     <row r="22" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8943,18 +8977,20 @@
       <c r="AJ22" s="56">
         <v>15.5</v>
       </c>
-      <c r="AK22" s="56"/>
+      <c r="AK22" s="56">
+        <v>15.3</v>
+      </c>
       <c r="AL22" s="56"/>
       <c r="AM22" s="56"/>
       <c r="AN22" s="56"/>
       <c r="AO22" s="56"/>
       <c r="AP22" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ22" s="71">
         <f t="shared" si="1"/>
-        <v>15.488461538461538</v>
+        <v>15.481481481481481</v>
       </c>
       <c r="AR22" s="71">
         <f>IFERROR(VLOOKUP(A22,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8962,7 +8998,7 @@
       </c>
       <c r="AS22" s="71">
         <f t="shared" si="2"/>
-        <v>1.7081286186931379</v>
+        <v>1.7011485617130813</v>
       </c>
     </row>
     <row r="23" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9074,18 +9110,20 @@
       <c r="AJ23" s="56">
         <v>25.5</v>
       </c>
-      <c r="AK23" s="56"/>
+      <c r="AK23" s="56">
+        <v>25.2</v>
+      </c>
       <c r="AL23" s="56"/>
       <c r="AM23" s="56"/>
       <c r="AN23" s="56"/>
       <c r="AO23" s="56"/>
       <c r="AP23" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ23" s="71">
         <f t="shared" si="1"/>
-        <v>26.092307692307688</v>
+        <v>26.059259259259257</v>
       </c>
       <c r="AR23" s="71" t="str">
         <f>IFERROR(VLOOKUP(A23,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9205,18 +9243,20 @@
       <c r="AJ24" s="56">
         <v>29.3</v>
       </c>
-      <c r="AK24" s="56"/>
+      <c r="AK24" s="56">
+        <v>29.3</v>
+      </c>
       <c r="AL24" s="56"/>
       <c r="AM24" s="56"/>
       <c r="AN24" s="56"/>
       <c r="AO24" s="56"/>
       <c r="AP24" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ24" s="71">
         <f t="shared" si="1"/>
-        <v>29.403846153846157</v>
+        <v>29.400000000000002</v>
       </c>
       <c r="AR24" s="71">
         <f>IFERROR(VLOOKUP(A24,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9224,7 +9264,7 @@
       </c>
       <c r="AS24" s="71">
         <f t="shared" si="2"/>
-        <v>1.0414876691100368</v>
+        <v>1.037641515263882</v>
       </c>
     </row>
     <row r="25" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9336,18 +9376,20 @@
       <c r="AJ25" s="56">
         <v>22.5</v>
       </c>
-      <c r="AK25" s="56"/>
+      <c r="AK25" s="56">
+        <v>21.2</v>
+      </c>
       <c r="AL25" s="56"/>
       <c r="AM25" s="56"/>
       <c r="AN25" s="56"/>
       <c r="AO25" s="56"/>
       <c r="AP25" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ25" s="71">
         <f t="shared" si="1"/>
-        <v>21.86538461538461</v>
+        <v>21.840740740740738</v>
       </c>
       <c r="AR25" s="71">
         <f>IFERROR(VLOOKUP(A25,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9355,7 +9397,7 @@
       </c>
       <c r="AS25" s="71">
         <f t="shared" si="2"/>
-        <v>1.9319601591824096</v>
+        <v>1.9073162845385383</v>
       </c>
     </row>
     <row r="26" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9467,18 +9509,20 @@
       <c r="AJ26" s="56">
         <v>10.9</v>
       </c>
-      <c r="AK26" s="56"/>
+      <c r="AK26" s="56">
+        <v>10.4</v>
+      </c>
       <c r="AL26" s="56"/>
       <c r="AM26" s="56"/>
       <c r="AN26" s="56"/>
       <c r="AO26" s="56"/>
       <c r="AP26" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ26" s="71">
         <f t="shared" si="1"/>
-        <v>11.576923076923075</v>
+        <v>11.53333333333333</v>
       </c>
       <c r="AR26" s="71">
         <f>IFERROR(VLOOKUP(A26,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9486,7 +9530,7 @@
       </c>
       <c r="AS26" s="71">
         <f t="shared" si="2"/>
-        <v>1.2066081767694854</v>
+        <v>1.1630184331797402</v>
       </c>
     </row>
     <row r="27" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9598,18 +9642,20 @@
       <c r="AJ27" s="56">
         <v>26.2</v>
       </c>
-      <c r="AK27" s="56"/>
+      <c r="AK27" s="56">
+        <v>28.1</v>
+      </c>
       <c r="AL27" s="56"/>
       <c r="AM27" s="56"/>
       <c r="AN27" s="56"/>
       <c r="AO27" s="56"/>
       <c r="AP27" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ27" s="71">
         <f t="shared" si="1"/>
-        <v>28.038461538461544</v>
+        <v>28.040740740740745</v>
       </c>
       <c r="AR27" s="71">
         <f>IFERROR(VLOOKUP(A27,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9617,7 +9663,7 @@
       </c>
       <c r="AS27" s="71">
         <f t="shared" si="2"/>
-        <v>1.0497555688656952</v>
+        <v>1.0520347711448963</v>
       </c>
     </row>
     <row r="28" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9729,18 +9775,20 @@
       <c r="AJ28" s="56">
         <v>23.7</v>
       </c>
-      <c r="AK28" s="56"/>
+      <c r="AK28" s="56">
+        <v>27.1</v>
+      </c>
       <c r="AL28" s="56"/>
       <c r="AM28" s="56"/>
       <c r="AN28" s="56"/>
       <c r="AO28" s="56"/>
       <c r="AP28" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ28" s="71">
         <f t="shared" si="1"/>
-        <v>26.488461538461539</v>
+        <v>26.511111111111113</v>
       </c>
       <c r="AR28" s="71">
         <f>IFERROR(VLOOKUP(A28,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9748,7 +9796,7 @@
       </c>
       <c r="AS28" s="71">
         <f t="shared" si="2"/>
-        <v>0.7370429869845978</v>
+        <v>0.75969255963417126</v>
       </c>
     </row>
     <row r="29" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9860,18 +9908,20 @@
       <c r="AJ29" s="56">
         <v>26.4</v>
       </c>
-      <c r="AK29" s="56"/>
+      <c r="AK29" s="56">
+        <v>28.6</v>
+      </c>
       <c r="AL29" s="56"/>
       <c r="AM29" s="56"/>
       <c r="AN29" s="56"/>
       <c r="AO29" s="56"/>
       <c r="AP29" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ29" s="71">
         <f t="shared" si="1"/>
-        <v>27.680769230769233</v>
+        <v>27.714814814814819</v>
       </c>
       <c r="AR29" s="71">
         <f>IFERROR(VLOOKUP(A29,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9879,7 +9929,7 @@
       </c>
       <c r="AS29" s="71">
         <f t="shared" si="2"/>
-        <v>0.7267270165119939</v>
+        <v>0.76077260055757989</v>
       </c>
     </row>
     <row r="30" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9991,18 +10041,20 @@
       <c r="AJ30" s="56">
         <v>25.8</v>
       </c>
-      <c r="AK30" s="56"/>
+      <c r="AK30" s="56">
+        <v>25.7</v>
+      </c>
       <c r="AL30" s="56"/>
       <c r="AM30" s="56"/>
       <c r="AN30" s="56"/>
       <c r="AO30" s="56"/>
       <c r="AP30" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ30" s="71">
         <f t="shared" si="1"/>
-        <v>25.284615384615385</v>
+        <v>25.3</v>
       </c>
       <c r="AR30" s="71">
         <f>IFERROR(VLOOKUP(A30,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10010,7 +10062,7 @@
       </c>
       <c r="AS30" s="71">
         <f t="shared" si="2"/>
-        <v>0.76661390148601427</v>
+        <v>0.7819985168706296</v>
       </c>
     </row>
     <row r="31" spans="1:45" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -10122,18 +10174,20 @@
       <c r="AJ31" s="98">
         <v>26.2</v>
       </c>
-      <c r="AK31" s="98"/>
+      <c r="AK31" s="98">
+        <v>26.2</v>
+      </c>
       <c r="AL31" s="98"/>
       <c r="AM31" s="98"/>
       <c r="AN31" s="98"/>
       <c r="AO31" s="98"/>
       <c r="AP31" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ31" s="71">
         <f t="shared" si="1"/>
-        <v>26.803846153846152</v>
+        <v>26.781481481481482</v>
       </c>
       <c r="AR31" s="71">
         <f>IFERROR(VLOOKUP(A31,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10141,7 +10195,7 @@
       </c>
       <c r="AS31" s="71">
         <f t="shared" si="2"/>
-        <v>1.4348975278007536</v>
+        <v>1.4125328554360834</v>
       </c>
     </row>
     <row r="32" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10253,18 +10307,20 @@
       <c r="AJ32" s="56">
         <v>19.266666666666669</v>
       </c>
-      <c r="AK32" s="56"/>
+      <c r="AK32" s="56">
+        <v>19.600000000000001</v>
+      </c>
       <c r="AL32" s="56"/>
       <c r="AM32" s="56"/>
       <c r="AN32" s="56"/>
       <c r="AO32" s="56"/>
       <c r="AP32" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ32" s="71">
         <f t="shared" si="1"/>
-        <v>20.49102564102564</v>
+        <v>20.458024691358023</v>
       </c>
       <c r="AR32" s="71">
         <f>IFERROR(VLOOKUP(A32,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10272,7 +10328,7 @@
       </c>
       <c r="AS32" s="71">
         <f t="shared" si="2"/>
-        <v>2.8341695889168008</v>
+        <v>2.8011686392491839</v>
       </c>
     </row>
     <row r="33" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10381,19 +10437,23 @@
       <c r="AI33" s="56">
         <v>29.2</v>
       </c>
-      <c r="AJ33" s="56"/>
-      <c r="AK33" s="56"/>
+      <c r="AJ33" s="56">
+        <v>26.95</v>
+      </c>
+      <c r="AK33" s="56">
+        <v>28.05</v>
+      </c>
       <c r="AL33" s="56"/>
       <c r="AM33" s="56"/>
       <c r="AN33" s="56"/>
       <c r="AO33" s="56"/>
       <c r="AP33" s="58">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AQ33" s="71">
         <f t="shared" si="1"/>
-        <v>27.940000000000005</v>
+        <v>27.907407407407412</v>
       </c>
       <c r="AR33" s="71">
         <f>IFERROR(VLOOKUP(A33,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10401,7 +10461,7 @@
       </c>
       <c r="AS33" s="71">
         <f t="shared" si="2"/>
-        <v>1.1125279187874533</v>
+        <v>1.0799353261948603</v>
       </c>
     </row>
     <row r="34" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10513,18 +10573,20 @@
       <c r="AJ34" s="56">
         <v>20.93333333333333</v>
       </c>
-      <c r="AK34" s="56"/>
+      <c r="AK34" s="56">
+        <v>21.266666666666669</v>
+      </c>
       <c r="AL34" s="56"/>
       <c r="AM34" s="56"/>
       <c r="AN34" s="56"/>
       <c r="AO34" s="56"/>
       <c r="AP34" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ34" s="71">
         <f t="shared" si="1"/>
-        <v>21.282051282051285</v>
+        <v>21.281481481481482</v>
       </c>
       <c r="AR34" s="71">
         <f>IFERROR(VLOOKUP(A34,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10532,7 +10594,7 @@
       </c>
       <c r="AS34" s="71">
         <f t="shared" si="2"/>
-        <v>1.4948536903709631</v>
+        <v>1.4942838898011601</v>
       </c>
     </row>
     <row r="35" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10644,18 +10706,20 @@
       <c r="AJ35" s="56">
         <v>24.7</v>
       </c>
-      <c r="AK35" s="56"/>
+      <c r="AK35" s="56">
+        <v>23.9</v>
+      </c>
       <c r="AL35" s="56"/>
       <c r="AM35" s="56"/>
       <c r="AN35" s="56"/>
       <c r="AO35" s="56"/>
       <c r="AP35" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ35" s="71">
         <f t="shared" si="1"/>
-        <v>24.548076923076923</v>
+        <v>24.524074074074072</v>
       </c>
       <c r="AR35" s="71">
         <f>IFERROR(VLOOKUP(A35,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10663,7 +10727,7 @@
       </c>
       <c r="AS35" s="71">
         <f t="shared" si="2"/>
-        <v>0.50982902335952218</v>
+        <v>0.48582617435667075</v>
       </c>
     </row>
     <row r="36" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10775,18 +10839,20 @@
       <c r="AJ36" s="56">
         <v>19</v>
       </c>
-      <c r="AK36" s="56"/>
+      <c r="AK36" s="56">
+        <v>19.649999999999999</v>
+      </c>
       <c r="AL36" s="56"/>
       <c r="AM36" s="56"/>
       <c r="AN36" s="56"/>
       <c r="AO36" s="56"/>
       <c r="AP36" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ36" s="71">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>19.987037037037037</v>
       </c>
       <c r="AR36" s="71">
         <f>IFERROR(VLOOKUP(A36,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10794,7 +10860,7 @@
       </c>
       <c r="AS36" s="71">
         <f t="shared" si="2"/>
-        <v>1.0011889367816096</v>
+        <v>0.98822597381864696</v>
       </c>
     </row>
     <row r="37" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10906,18 +10972,20 @@
       <c r="AJ37" s="56">
         <v>26.8</v>
       </c>
-      <c r="AK37" s="56"/>
+      <c r="AK37" s="56">
+        <v>27.3</v>
+      </c>
       <c r="AL37" s="56"/>
       <c r="AM37" s="56"/>
       <c r="AN37" s="56"/>
       <c r="AO37" s="56"/>
       <c r="AP37" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ37" s="71">
         <f t="shared" si="1"/>
-        <v>27.371153846153849</v>
+        <v>27.36851851851852</v>
       </c>
       <c r="AR37" s="71">
         <f>IFERROR(VLOOKUP(A37,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10925,7 +10993,7 @@
       </c>
       <c r="AS37" s="71">
         <f t="shared" si="2"/>
-        <v>1.4849239722164675</v>
+        <v>1.4822886445811392</v>
       </c>
     </row>
     <row r="38" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11033,18 +11101,20 @@
       <c r="AJ38" s="56">
         <v>15.15</v>
       </c>
-      <c r="AK38" s="56"/>
+      <c r="AK38" s="56">
+        <v>15.05</v>
+      </c>
       <c r="AL38" s="56"/>
       <c r="AM38" s="56"/>
       <c r="AN38" s="56"/>
       <c r="AO38" s="56"/>
       <c r="AP38" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ38" s="71">
         <f t="shared" si="1"/>
-        <v>15.939583333333331</v>
+        <v>15.903999999999998</v>
       </c>
       <c r="AR38" s="71">
         <f>IFERROR(VLOOKUP(A38,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11052,7 +11122,7 @@
       </c>
       <c r="AS38" s="71">
         <f t="shared" si="2"/>
-        <v>0.92165432638265088</v>
+        <v>0.88607099304931758</v>
       </c>
     </row>
     <row r="39" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11162,18 +11232,20 @@
       <c r="AJ39" s="56">
         <v>20.666666666666671</v>
       </c>
-      <c r="AK39" s="56"/>
+      <c r="AK39" s="56">
+        <v>21.06666666666667</v>
+      </c>
       <c r="AL39" s="56"/>
       <c r="AM39" s="56"/>
       <c r="AN39" s="56"/>
       <c r="AO39" s="56"/>
       <c r="AP39" s="58">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ39" s="71">
         <f t="shared" si="1"/>
-        <v>22.261333333333333</v>
+        <v>22.215384615384615</v>
       </c>
       <c r="AR39" s="71" t="str">
         <f>IFERROR(VLOOKUP(A39,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11281,18 +11353,20 @@
       <c r="AJ40" s="56">
         <v>23.333333333333329</v>
       </c>
-      <c r="AK40" s="56"/>
+      <c r="AK40" s="56">
+        <v>24.733333333333331</v>
+      </c>
       <c r="AL40" s="56"/>
       <c r="AM40" s="56"/>
       <c r="AN40" s="56"/>
       <c r="AO40" s="56"/>
       <c r="AP40" s="58">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ40" s="71">
         <f t="shared" si="1"/>
-        <v>25.217499999999994</v>
+        <v>25.194444444444439</v>
       </c>
       <c r="AR40" s="71">
         <f>IFERROR(VLOOKUP(A40,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11300,7 +11374,7 @@
       </c>
       <c r="AS40" s="71">
         <f t="shared" si="2"/>
-        <v>2.3657092515730227</v>
+        <v>2.342653696017468</v>
       </c>
     </row>
     <row r="41" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11410,18 +11484,20 @@
       <c r="AJ41" s="56">
         <v>19.2</v>
       </c>
-      <c r="AK41" s="56"/>
+      <c r="AK41" s="56">
+        <v>18.86666666666666</v>
+      </c>
       <c r="AL41" s="56"/>
       <c r="AM41" s="56"/>
       <c r="AN41" s="56"/>
       <c r="AO41" s="56"/>
       <c r="AP41" s="58">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ41" s="71">
         <f t="shared" si="1"/>
-        <v>20.147999999999996</v>
+        <v>20.09871794871794</v>
       </c>
       <c r="AR41" s="71">
         <f>IFERROR(VLOOKUP(A41,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11429,7 +11505,7 @@
       </c>
       <c r="AS41" s="71">
         <f t="shared" si="2"/>
-        <v>1.6558908086722575</v>
+        <v>1.6066087573902017</v>
       </c>
     </row>
     <row r="42" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11541,18 +11617,20 @@
       <c r="AJ42" s="56">
         <v>27.15</v>
       </c>
-      <c r="AK42" s="56"/>
+      <c r="AK42" s="56">
+        <v>26.9</v>
+      </c>
       <c r="AL42" s="56"/>
       <c r="AM42" s="56"/>
       <c r="AN42" s="56"/>
       <c r="AO42" s="56"/>
       <c r="AP42" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ42" s="71">
         <f t="shared" si="1"/>
-        <v>27.987499999999997</v>
+        <v>27.947222222222219</v>
       </c>
       <c r="AR42" s="71">
         <f>IFERROR(VLOOKUP(A42,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11560,7 +11638,7 @@
       </c>
       <c r="AS42" s="71">
         <f t="shared" si="2"/>
-        <v>0.2348144829417258</v>
+        <v>0.19453670516394794</v>
       </c>
     </row>
     <row r="43" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11668,18 +11746,20 @@
       <c r="AJ43" s="56">
         <v>28.1</v>
       </c>
-      <c r="AK43" s="56"/>
+      <c r="AK43" s="56">
+        <v>28.15</v>
+      </c>
       <c r="AL43" s="56"/>
       <c r="AM43" s="56"/>
       <c r="AN43" s="56"/>
       <c r="AO43" s="56"/>
       <c r="AP43" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ43" s="71">
         <f t="shared" si="1"/>
-        <v>29.32083333333334</v>
+        <v>29.274000000000004</v>
       </c>
       <c r="AR43" s="71" t="str">
         <f>IFERROR(VLOOKUP(A43,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11799,18 +11879,20 @@
       <c r="AJ44" s="56">
         <v>29.1</v>
       </c>
-      <c r="AK44" s="56"/>
+      <c r="AK44" s="56">
+        <v>27.875</v>
+      </c>
       <c r="AL44" s="56"/>
       <c r="AM44" s="56"/>
       <c r="AN44" s="56"/>
       <c r="AO44" s="56"/>
       <c r="AP44" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ44" s="71">
         <f t="shared" si="1"/>
-        <v>28.527884615384611</v>
+        <v>28.5037037037037</v>
       </c>
       <c r="AR44" s="71">
         <f>IFERROR(VLOOKUP(A44,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11818,7 +11900,7 @@
       </c>
       <c r="AS44" s="71">
         <f t="shared" si="2"/>
-        <v>1.1855411711017894</v>
+        <v>1.1613602594208778</v>
       </c>
     </row>
     <row r="45" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11930,18 +12012,20 @@
       <c r="AJ45" s="56">
         <v>27.75</v>
       </c>
-      <c r="AK45" s="56"/>
+      <c r="AK45" s="56">
+        <v>27.2</v>
+      </c>
       <c r="AL45" s="56"/>
       <c r="AM45" s="56"/>
       <c r="AN45" s="56"/>
       <c r="AO45" s="56"/>
       <c r="AP45" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ45" s="71">
         <f t="shared" si="1"/>
-        <v>29.24038461538462</v>
+        <v>29.164814814814822</v>
       </c>
       <c r="AR45" s="71">
         <f>IFERROR(VLOOKUP(A45,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11949,7 +12033,7 @@
       </c>
       <c r="AS45" s="71">
         <f t="shared" si="2"/>
-        <v>1.4722771404531905</v>
+        <v>1.3967073398833918</v>
       </c>
     </row>
     <row r="46" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12061,18 +12145,20 @@
       <c r="AJ46" s="56">
         <v>28.1</v>
       </c>
-      <c r="AK46" s="56"/>
+      <c r="AK46" s="56">
+        <v>27.7</v>
+      </c>
       <c r="AL46" s="56"/>
       <c r="AM46" s="56"/>
       <c r="AN46" s="56"/>
       <c r="AO46" s="56"/>
       <c r="AP46" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ46" s="71">
         <f t="shared" si="1"/>
-        <v>28.929807692307691</v>
+        <v>28.88425925925926</v>
       </c>
       <c r="AR46" s="71">
         <f>IFERROR(VLOOKUP(A46,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12080,7 +12166,7 @@
       </c>
       <c r="AS46" s="71">
         <f t="shared" si="2"/>
-        <v>1.0236100604102099</v>
+        <v>0.97806162736177882</v>
       </c>
     </row>
     <row r="47" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12192,18 +12278,20 @@
       <c r="AJ47" s="56">
         <v>28.6</v>
       </c>
-      <c r="AK47" s="56"/>
+      <c r="AK47" s="56">
+        <v>27.666666666666671</v>
+      </c>
       <c r="AL47" s="56"/>
       <c r="AM47" s="56"/>
       <c r="AN47" s="56"/>
       <c r="AO47" s="56"/>
       <c r="AP47" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ47" s="71">
         <f t="shared" si="1"/>
-        <v>29.952564102564111</v>
+        <v>29.867901234567906</v>
       </c>
       <c r="AR47" s="71">
         <f>IFERROR(VLOOKUP(A47,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12211,7 +12299,7 @@
       </c>
       <c r="AS47" s="71">
         <f t="shared" si="2"/>
-        <v>1.9836882432467213</v>
+        <v>1.8990253752505168</v>
       </c>
     </row>
     <row r="48" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12481,18 +12569,20 @@
       <c r="AJ50" s="56">
         <v>27.75</v>
       </c>
-      <c r="AK50" s="56"/>
+      <c r="AK50" s="56">
+        <v>28.4</v>
+      </c>
       <c r="AL50" s="56"/>
       <c r="AM50" s="56"/>
       <c r="AN50" s="56"/>
       <c r="AO50" s="56"/>
       <c r="AP50" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ50" s="71">
         <f t="shared" si="1"/>
-        <v>29.213461538461537</v>
+        <v>29.18333333333333</v>
       </c>
       <c r="AR50" s="71">
         <f>IFERROR(VLOOKUP(A50,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12500,7 +12590,7 @@
       </c>
       <c r="AS50" s="71">
         <f t="shared" si="2"/>
-        <v>1.9247711924297164</v>
+        <v>1.8946429873015092</v>
       </c>
     </row>
     <row r="51" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12798,18 +12888,20 @@
       <c r="AJ53" s="56">
         <v>27.65</v>
       </c>
-      <c r="AK53" s="56"/>
+      <c r="AK53" s="56">
+        <v>27</v>
+      </c>
       <c r="AL53" s="56"/>
       <c r="AM53" s="56"/>
       <c r="AN53" s="56"/>
       <c r="AO53" s="56"/>
       <c r="AP53" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ53" s="71">
         <f t="shared" si="1"/>
-        <v>28.886538461538461</v>
+        <v>28.816666666666666</v>
       </c>
       <c r="AR53" s="71">
         <f>IFERROR(VLOOKUP(A53,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12817,7 +12909,7 @@
       </c>
       <c r="AS53" s="71">
         <f t="shared" si="2"/>
-        <v>1.5272921649479123</v>
+        <v>1.4574203700761181</v>
       </c>
     </row>
     <row r="54" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12929,18 +13021,20 @@
       <c r="AJ54" s="56">
         <v>27.35</v>
       </c>
-      <c r="AK54" s="56"/>
+      <c r="AK54" s="56">
+        <v>28.7</v>
+      </c>
       <c r="AL54" s="56"/>
       <c r="AM54" s="56"/>
       <c r="AN54" s="56"/>
       <c r="AO54" s="56"/>
       <c r="AP54" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ54" s="71">
         <f t="shared" si="1"/>
-        <v>30.030769230769238</v>
+        <v>29.981481481481492</v>
       </c>
       <c r="AR54" s="71">
         <f>IFERROR(VLOOKUP(A54,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12948,7 +13042,7 @@
       </c>
       <c r="AS54" s="71">
         <f t="shared" si="2"/>
-        <v>1.5325432057028188</v>
+        <v>1.4832554564150726</v>
       </c>
     </row>
     <row r="55" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13046,18 +13140,20 @@
       <c r="AJ55" s="56">
         <v>29.95</v>
       </c>
-      <c r="AK55" s="56"/>
+      <c r="AK55" s="56">
+        <v>27.2</v>
+      </c>
       <c r="AL55" s="56"/>
       <c r="AM55" s="56"/>
       <c r="AN55" s="56"/>
       <c r="AO55" s="56"/>
       <c r="AP55" s="58">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ55" s="71">
         <f t="shared" si="1"/>
-        <v>30.297368421052635</v>
+        <v>30.142500000000005</v>
       </c>
       <c r="AR55" s="71">
         <f>IFERROR(VLOOKUP(A55,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13065,7 +13161,7 @@
       </c>
       <c r="AS55" s="71">
         <f t="shared" si="2"/>
-        <v>1.8664087508155944</v>
+        <v>1.7115403297629648</v>
       </c>
     </row>
     <row r="56" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13177,18 +13273,20 @@
       <c r="AJ56" s="56">
         <v>27.35</v>
       </c>
-      <c r="AK56" s="56"/>
+      <c r="AK56" s="56">
+        <v>27.45</v>
+      </c>
       <c r="AL56" s="56"/>
       <c r="AM56" s="56"/>
       <c r="AN56" s="56"/>
       <c r="AO56" s="56"/>
       <c r="AP56" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ56" s="71">
         <f t="shared" si="1"/>
-        <v>29.384615384615383</v>
+        <v>29.312962962962963</v>
       </c>
       <c r="AR56" s="71" t="str">
         <f>IFERROR(VLOOKUP(A56,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13464,18 +13562,20 @@
       <c r="AJ59" s="56">
         <v>28.15</v>
       </c>
-      <c r="AK59" s="56"/>
+      <c r="AK59" s="56">
+        <v>27.6</v>
+      </c>
       <c r="AL59" s="56"/>
       <c r="AM59" s="56"/>
       <c r="AN59" s="56"/>
       <c r="AO59" s="56"/>
       <c r="AP59" s="58">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ59" s="71">
         <f t="shared" si="1"/>
-        <v>29.061</v>
+        <v>29.004807692307693</v>
       </c>
       <c r="AR59" s="71">
         <f>IFERROR(VLOOKUP(A59,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13483,7 +13583,7 @@
       </c>
       <c r="AS59" s="71">
         <f t="shared" si="2"/>
-        <v>0.94678017091784028</v>
+        <v>0.89058786322553374</v>
       </c>
     </row>
     <row r="60" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13585,18 +13685,20 @@
       <c r="AJ60" s="56">
         <v>25.5</v>
       </c>
-      <c r="AK60" s="56"/>
+      <c r="AK60" s="56">
+        <v>25.95</v>
+      </c>
       <c r="AL60" s="56"/>
       <c r="AM60" s="56"/>
       <c r="AN60" s="56"/>
       <c r="AO60" s="56"/>
       <c r="AP60" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ60" s="71">
         <f t="shared" si="1"/>
-        <v>25.721428571428572</v>
+        <v>25.731818181818184</v>
       </c>
       <c r="AR60" s="71">
         <f>IFERROR(VLOOKUP(A60,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13604,7 +13706,7 @@
       </c>
       <c r="AS60" s="71">
         <f t="shared" si="2"/>
-        <v>1.5768643564802431</v>
+        <v>1.5872539668698558</v>
       </c>
     </row>
     <row r="61" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13716,18 +13818,20 @@
       <c r="AJ61" s="56">
         <v>26.9</v>
       </c>
-      <c r="AK61" s="56"/>
+      <c r="AK61" s="56">
+        <v>27.2</v>
+      </c>
       <c r="AL61" s="56"/>
       <c r="AM61" s="56"/>
       <c r="AN61" s="56"/>
       <c r="AO61" s="56"/>
       <c r="AP61" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ61" s="71">
         <f t="shared" si="1"/>
-        <v>26.676923076923082</v>
+        <v>26.696296296296303</v>
       </c>
       <c r="AR61" s="71">
         <f>IFERROR(VLOOKUP(A61,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13735,7 +13839,7 @@
       </c>
       <c r="AS61" s="71">
         <f t="shared" si="2"/>
-        <v>0.97025139519712056</v>
+        <v>0.98962461457034223</v>
       </c>
     </row>
     <row r="62" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13847,18 +13951,20 @@
       <c r="AJ62" s="56">
         <v>25.86666666666666</v>
       </c>
-      <c r="AK62" s="56"/>
+      <c r="AK62" s="56">
+        <v>26.6</v>
+      </c>
       <c r="AL62" s="56"/>
       <c r="AM62" s="56"/>
       <c r="AN62" s="56"/>
       <c r="AO62" s="56"/>
       <c r="AP62" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ62" s="71">
         <f t="shared" si="1"/>
-        <v>25.933333333333337</v>
+        <v>25.95802469135803</v>
       </c>
       <c r="AR62" s="71">
         <f>IFERROR(VLOOKUP(A62,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13866,7 +13972,7 @@
       </c>
       <c r="AS62" s="71">
         <f t="shared" si="2"/>
-        <v>1.3943293933694463</v>
+        <v>1.4190207513941395</v>
       </c>
     </row>
     <row r="63" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14118,18 +14224,20 @@
       <c r="AJ65" s="56">
         <v>25.2</v>
       </c>
-      <c r="AK65" s="56"/>
+      <c r="AK65" s="56">
+        <v>25.7</v>
+      </c>
       <c r="AL65" s="56"/>
       <c r="AM65" s="56"/>
       <c r="AN65" s="56"/>
       <c r="AO65" s="56"/>
       <c r="AP65" s="58">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ65" s="71">
         <f t="shared" si="1"/>
-        <v>25.74117647058824</v>
+        <v>25.738888888888894</v>
       </c>
       <c r="AR65" s="71">
         <f>IFERROR(VLOOKUP(A65,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14137,7 +14245,7 @@
       </c>
       <c r="AS65" s="71">
         <f t="shared" si="2"/>
-        <v>0.73597051227708121</v>
+        <v>0.7336829305777357</v>
       </c>
     </row>
     <row r="66" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14249,18 +14357,20 @@
       <c r="AJ66" s="56">
         <v>25.5</v>
       </c>
-      <c r="AK66" s="56"/>
+      <c r="AK66" s="56">
+        <v>26.95</v>
+      </c>
       <c r="AL66" s="56"/>
       <c r="AM66" s="56"/>
       <c r="AN66" s="56"/>
       <c r="AO66" s="56"/>
       <c r="AP66" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ66" s="71">
         <f t="shared" si="1"/>
-        <v>25.642307692307686</v>
+        <v>25.690740740740736</v>
       </c>
       <c r="AR66" s="71">
         <f>IFERROR(VLOOKUP(A66,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14268,7 +14378,7 @@
       </c>
       <c r="AS66" s="71">
         <f t="shared" si="2"/>
-        <v>0.73319286202869449</v>
+        <v>0.78162591046174512</v>
       </c>
     </row>
     <row r="67" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14376,18 +14486,20 @@
       <c r="AJ67" s="56">
         <v>24.55</v>
       </c>
-      <c r="AK67" s="56"/>
+      <c r="AK67" s="56">
+        <v>28.15</v>
+      </c>
       <c r="AL67" s="56"/>
       <c r="AM67" s="56"/>
       <c r="AN67" s="56"/>
       <c r="AO67" s="56"/>
       <c r="AP67" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ67" s="71">
         <f t="shared" si="1"/>
-        <v>25.429166666666664</v>
+        <v>25.537999999999997</v>
       </c>
       <c r="AR67" s="71">
         <f>IFERROR(VLOOKUP(A67,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14395,7 +14507,7 @@
       </c>
       <c r="AS67" s="71">
         <f t="shared" si="2"/>
-        <v>0.77795975483545377</v>
+        <v>0.88679308816878688</v>
       </c>
     </row>
     <row r="68" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14507,18 +14619,20 @@
       <c r="AJ68" s="56">
         <v>26.95</v>
       </c>
-      <c r="AK68" s="56"/>
+      <c r="AK68" s="56">
+        <v>26.25</v>
+      </c>
       <c r="AL68" s="56"/>
       <c r="AM68" s="56"/>
       <c r="AN68" s="56"/>
       <c r="AO68" s="56"/>
       <c r="AP68" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ68" s="71">
         <f t="shared" si="1"/>
-        <v>25.505769230769229</v>
+        <v>25.533333333333331</v>
       </c>
       <c r="AR68" s="71">
         <f>IFERROR(VLOOKUP(A68,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14526,7 +14640,7 @@
       </c>
       <c r="AS68" s="71">
         <f t="shared" si="2"/>
-        <v>0.98068172802620879</v>
+        <v>1.0082458305903117</v>
       </c>
     </row>
     <row r="69" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14638,18 +14752,20 @@
       <c r="AJ69" s="56">
         <v>24.824999999999999</v>
       </c>
-      <c r="AK69" s="56"/>
+      <c r="AK69" s="56">
+        <v>25.25</v>
+      </c>
       <c r="AL69" s="56"/>
       <c r="AM69" s="56"/>
       <c r="AN69" s="56"/>
       <c r="AO69" s="56"/>
       <c r="AP69" s="58">
         <f t="shared" ref="AP69:AP132" si="3">COUNTIF(K69:AO69,"&gt;0")</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ69" s="71">
         <f t="shared" ref="AQ69:AQ132" si="4">IF(AP69&gt;14,AVERAGE(K69:AO69),"")</f>
-        <v>24.950961538461545</v>
+        <v>24.962037037037042</v>
       </c>
       <c r="AR69" s="71">
         <f>IFERROR(VLOOKUP(A69,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14657,7 +14773,7 @@
       </c>
       <c r="AS69" s="71">
         <f t="shared" ref="AS69:AS132" si="5">IF(OR(AQ69="",AR69=""),"",IFERROR(AQ69-AR69,""))</f>
-        <v>0.62856385182953645</v>
+        <v>0.63963935040503372</v>
       </c>
     </row>
     <row r="70" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14755,18 +14871,20 @@
       <c r="AJ70" s="56">
         <v>26.466666666666669</v>
       </c>
-      <c r="AK70" s="56"/>
+      <c r="AK70" s="56">
+        <v>26.666666666666671</v>
+      </c>
       <c r="AL70" s="56"/>
       <c r="AM70" s="56"/>
       <c r="AN70" s="56"/>
       <c r="AO70" s="56"/>
       <c r="AP70" s="58">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ70" s="71">
         <f t="shared" si="4"/>
-        <v>26.49649122807018</v>
+        <v>26.505000000000003</v>
       </c>
       <c r="AR70" s="71">
         <f>IFERROR(VLOOKUP(A70,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14774,7 +14892,7 @@
       </c>
       <c r="AS70" s="71">
         <f t="shared" si="5"/>
-        <v>0.92653253702697924</v>
+        <v>0.93504130895680149</v>
       </c>
     </row>
     <row r="71" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14886,18 +15004,20 @@
       <c r="AJ71" s="56">
         <v>24.966666666666669</v>
       </c>
-      <c r="AK71" s="56"/>
+      <c r="AK71" s="56">
+        <v>26.4</v>
+      </c>
       <c r="AL71" s="56"/>
       <c r="AM71" s="56"/>
       <c r="AN71" s="56"/>
       <c r="AO71" s="56"/>
       <c r="AP71" s="58">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ71" s="71">
         <f t="shared" si="4"/>
-        <v>25.907692307692308</v>
+        <v>25.925925925925927</v>
       </c>
       <c r="AR71" s="71">
         <f>IFERROR(VLOOKUP(A71,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14905,7 +15025,7 @@
       </c>
       <c r="AS71" s="71">
         <f t="shared" si="5"/>
-        <v>0.24524939403877966</v>
+        <v>0.26348301227239901</v>
       </c>
     </row>
     <row r="72" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15015,18 +15135,20 @@
       <c r="AJ72" s="56">
         <v>26.9</v>
       </c>
-      <c r="AK72" s="56"/>
+      <c r="AK72" s="56">
+        <v>24.06666666666667</v>
+      </c>
       <c r="AL72" s="56"/>
       <c r="AM72" s="56"/>
       <c r="AN72" s="56"/>
       <c r="AO72" s="56"/>
       <c r="AP72" s="58">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ72" s="71">
         <f t="shared" si="4"/>
-        <v>25.508000000000003</v>
+        <v>25.452564102564107</v>
       </c>
       <c r="AR72" s="71">
         <f>IFERROR(VLOOKUP(A72,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15034,7 +15156,7 @@
       </c>
       <c r="AS72" s="71">
         <f t="shared" si="5"/>
-        <v>0.53479125704046382</v>
+        <v>0.47935535960456832</v>
       </c>
     </row>
     <row r="73" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15130,18 +15252,20 @@
       </c>
       <c r="AI73" s="56"/>
       <c r="AJ73" s="56"/>
-      <c r="AK73" s="56"/>
+      <c r="AK73" s="56">
+        <v>26.35</v>
+      </c>
       <c r="AL73" s="56"/>
       <c r="AM73" s="56"/>
       <c r="AN73" s="56"/>
       <c r="AO73" s="56"/>
       <c r="AP73" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ73" s="71">
         <f t="shared" si="4"/>
-        <v>25.755555555555553</v>
+        <v>25.786842105263158</v>
       </c>
       <c r="AR73" s="71" t="str">
         <f>IFERROR(VLOOKUP(A73,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15261,18 +15385,20 @@
       <c r="AJ74" s="56">
         <v>22.1</v>
       </c>
-      <c r="AK74" s="56"/>
+      <c r="AK74" s="56">
+        <v>20.55</v>
+      </c>
       <c r="AL74" s="56"/>
       <c r="AM74" s="56"/>
       <c r="AN74" s="56"/>
       <c r="AO74" s="56"/>
       <c r="AP74" s="58">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ74" s="71">
         <f t="shared" si="4"/>
-        <v>20.848076923076924</v>
+        <v>20.837037037037039</v>
       </c>
       <c r="AR74" s="71">
         <f>IFERROR(VLOOKUP(A74,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15280,7 +15406,7 @@
       </c>
       <c r="AS74" s="71">
         <f t="shared" si="5"/>
-        <v>0.84957817371681443</v>
+        <v>0.83853828767692917</v>
       </c>
     </row>
     <row r="75" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15392,18 +15518,20 @@
       <c r="AJ75" s="56">
         <v>14.46666666666667</v>
       </c>
-      <c r="AK75" s="56"/>
+      <c r="AK75" s="56">
+        <v>15.866666666666671</v>
+      </c>
       <c r="AL75" s="56"/>
       <c r="AM75" s="56"/>
       <c r="AN75" s="56"/>
       <c r="AO75" s="56"/>
       <c r="AP75" s="58">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ75" s="71">
         <f t="shared" si="4"/>
-        <v>15.829487179487176</v>
+        <v>15.830864197530859</v>
       </c>
       <c r="AR75" s="71">
         <f>IFERROR(VLOOKUP(A75,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15411,7 +15539,7 @@
       </c>
       <c r="AS75" s="71">
         <f t="shared" si="5"/>
-        <v>0.64844348752038528</v>
+        <v>0.6498205055640689</v>
       </c>
     </row>
     <row r="76" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15523,18 +15651,20 @@
       <c r="AJ76" s="56">
         <v>20.149999999999999</v>
       </c>
-      <c r="AK76" s="56"/>
+      <c r="AK76" s="56">
+        <v>20.149999999999999</v>
+      </c>
       <c r="AL76" s="56"/>
       <c r="AM76" s="56"/>
       <c r="AN76" s="56"/>
       <c r="AO76" s="56"/>
       <c r="AP76" s="58">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ76" s="71">
         <f t="shared" si="4"/>
-        <v>20.716346153846153</v>
+        <v>20.69537037037037</v>
       </c>
       <c r="AR76" s="71">
         <f>IFERROR(VLOOKUP(A76,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15542,7 +15672,7 @@
       </c>
       <c r="AS76" s="71">
         <f t="shared" si="5"/>
-        <v>0.9163795423199339</v>
+        <v>0.89540375884415013</v>
       </c>
     </row>
     <row r="77" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15654,18 +15784,20 @@
       <c r="AJ77" s="56">
         <v>23.8</v>
       </c>
-      <c r="AK77" s="56"/>
+      <c r="AK77" s="56">
+        <v>25.733333333333331</v>
+      </c>
       <c r="AL77" s="56"/>
       <c r="AM77" s="56"/>
       <c r="AN77" s="56"/>
       <c r="AO77" s="56"/>
       <c r="AP77" s="58">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ77" s="71">
         <f t="shared" si="4"/>
-        <v>23.907692307692301</v>
+        <v>23.975308641975303</v>
       </c>
       <c r="AR77" s="71">
         <f>IFERROR(VLOOKUP(A77,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15673,7 +15805,7 @@
       </c>
       <c r="AS77" s="71">
         <f t="shared" si="5"/>
-        <v>1.2244514517133815</v>
+        <v>1.2920677859963838</v>
       </c>
     </row>
     <row r="78" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15912,18 +16044,20 @@
       <c r="AJ79" s="56">
         <v>31.333333333333329</v>
       </c>
-      <c r="AK79" s="56"/>
+      <c r="AK79" s="56">
+        <v>32.4</v>
+      </c>
       <c r="AL79" s="56"/>
       <c r="AM79" s="56"/>
       <c r="AN79" s="56"/>
       <c r="AO79" s="56"/>
       <c r="AP79" s="58">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ79" s="71">
         <f t="shared" si="4"/>
-        <v>31.197222222222219</v>
+        <v>31.245333333333328</v>
       </c>
       <c r="AR79" s="71">
         <f>IFERROR(VLOOKUP(A79,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15931,7 +16065,7 @@
       </c>
       <c r="AS79" s="71">
         <f t="shared" si="5"/>
-        <v>1.7281693377714902</v>
+        <v>1.7762804488825985</v>
       </c>
     </row>
     <row r="80" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16166,18 +16300,20 @@
       <c r="AJ81" s="56">
         <v>25.55</v>
       </c>
-      <c r="AK81" s="56"/>
+      <c r="AK81" s="56">
+        <v>25.15</v>
+      </c>
       <c r="AL81" s="56"/>
       <c r="AM81" s="56"/>
       <c r="AN81" s="56"/>
       <c r="AO81" s="56"/>
       <c r="AP81" s="58">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ81" s="71">
         <f t="shared" si="4"/>
-        <v>24.126086956521732</v>
+        <v>24.168749999999992</v>
       </c>
       <c r="AR81" s="71">
         <f>IFERROR(VLOOKUP(A81,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16185,7 +16321,7 @@
       </c>
       <c r="AS81" s="71">
         <f t="shared" si="5"/>
-        <v>-4.8542949570038019E-2</v>
+        <v>-5.8799060917777979E-3</v>
       </c>
     </row>
     <row r="82" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16568,18 +16704,20 @@
       <c r="AJ85" s="56">
         <v>30.45</v>
       </c>
-      <c r="AK85" s="56"/>
+      <c r="AK85" s="56">
+        <v>30.05</v>
+      </c>
       <c r="AL85" s="56"/>
       <c r="AM85" s="56"/>
       <c r="AN85" s="56"/>
       <c r="AO85" s="56"/>
       <c r="AP85" s="58">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ85" s="71">
         <f t="shared" si="4"/>
-        <v>30.847058823529409</v>
+        <v>30.802777777777774</v>
       </c>
       <c r="AR85" s="71" t="str">
         <f>IFERROR(VLOOKUP(A85,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16699,18 +16837,20 @@
       <c r="AJ86" s="56">
         <v>30.05</v>
       </c>
-      <c r="AK86" s="56"/>
+      <c r="AK86" s="56">
+        <v>29.5</v>
+      </c>
       <c r="AL86" s="56"/>
       <c r="AM86" s="56"/>
       <c r="AN86" s="56"/>
       <c r="AO86" s="56"/>
       <c r="AP86" s="58">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ86" s="71">
         <f t="shared" si="4"/>
-        <v>29.761538461538457</v>
+        <v>29.751851851851846</v>
       </c>
       <c r="AR86" s="71">
         <f>IFERROR(VLOOKUP(A86,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16718,7 +16858,7 @@
       </c>
       <c r="AS86" s="71">
         <f t="shared" si="5"/>
-        <v>1.1494552999836678</v>
+        <v>1.139768690297057</v>
       </c>
     </row>
     <row r="87" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16830,18 +16970,20 @@
       <c r="AJ87" s="56">
         <v>27.1</v>
       </c>
-      <c r="AK87" s="56"/>
+      <c r="AK87" s="56">
+        <v>29.45</v>
+      </c>
       <c r="AL87" s="56"/>
       <c r="AM87" s="56"/>
       <c r="AN87" s="56"/>
       <c r="AO87" s="56"/>
       <c r="AP87" s="58">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ87" s="71">
         <f t="shared" si="4"/>
-        <v>31.650000000000002</v>
+        <v>31.568518518518523</v>
       </c>
       <c r="AR87" s="71">
         <f>IFERROR(VLOOKUP(A87,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16849,7 +16991,7 @@
       </c>
       <c r="AS87" s="71">
         <f t="shared" si="5"/>
-        <v>2.6438100275376115</v>
+        <v>2.5623285460561327</v>
       </c>
     </row>
     <row r="88" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16961,18 +17103,20 @@
       <c r="AJ88" s="56">
         <v>28.65</v>
       </c>
-      <c r="AK88" s="56"/>
+      <c r="AK88" s="56">
+        <v>30.25</v>
+      </c>
       <c r="AL88" s="56"/>
       <c r="AM88" s="56"/>
       <c r="AN88" s="56"/>
       <c r="AO88" s="56"/>
       <c r="AP88" s="58">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ88" s="71">
         <f t="shared" si="4"/>
-        <v>30.130769230769236</v>
+        <v>30.13518518518519</v>
       </c>
       <c r="AR88" s="71">
         <f>IFERROR(VLOOKUP(A88,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16980,7 +17124,7 @@
       </c>
       <c r="AS88" s="71">
         <f t="shared" si="5"/>
-        <v>1.4398946147938254</v>
+        <v>1.4443105692097795</v>
       </c>
     </row>
     <row r="89" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17080,18 +17224,20 @@
       <c r="AJ89" s="56">
         <v>28.65</v>
       </c>
-      <c r="AK89" s="56"/>
+      <c r="AK89" s="56">
+        <v>31.7</v>
+      </c>
       <c r="AL89" s="56"/>
       <c r="AM89" s="56"/>
       <c r="AN89" s="56"/>
       <c r="AO89" s="56"/>
       <c r="AP89" s="58">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ89" s="71">
         <f t="shared" si="4"/>
-        <v>33.239999999999995</v>
+        <v>33.166666666666664</v>
       </c>
       <c r="AR89" s="71">
         <f>IFERROR(VLOOKUP(A89,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17099,7 +17245,7 @@
       </c>
       <c r="AS89" s="71">
         <f t="shared" si="5"/>
-        <v>3.7575009583532939</v>
+        <v>3.6841676250199633</v>
       </c>
     </row>
     <row r="90" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17203,18 +17349,20 @@
       <c r="AJ90" s="56">
         <v>31.25</v>
       </c>
-      <c r="AK90" s="56"/>
+      <c r="AK90" s="56">
+        <v>29.35</v>
+      </c>
       <c r="AL90" s="56"/>
       <c r="AM90" s="56"/>
       <c r="AN90" s="56"/>
       <c r="AO90" s="56"/>
       <c r="AP90" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ90" s="71">
         <f t="shared" si="4"/>
-        <v>32.072727272727271</v>
+        <v>31.954347826086959</v>
       </c>
       <c r="AR90" s="71">
         <f>IFERROR(VLOOKUP(A90,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17222,7 +17370,7 @@
       </c>
       <c r="AS90" s="71">
         <f t="shared" si="5"/>
-        <v>3.0376672148146113</v>
+        <v>2.9192877681742999</v>
       </c>
     </row>
     <row r="91" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17449,18 +17597,20 @@
       <c r="AJ92" s="56">
         <v>17.2</v>
       </c>
-      <c r="AK92" s="56"/>
+      <c r="AK92" s="56">
+        <v>16.2</v>
+      </c>
       <c r="AL92" s="56"/>
       <c r="AM92" s="56"/>
       <c r="AN92" s="56"/>
       <c r="AO92" s="56"/>
       <c r="AP92" s="58">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ92" s="71">
         <f t="shared" si="4"/>
-        <v>17.549358974358977</v>
+        <v>17.499382716049386</v>
       </c>
       <c r="AR92" s="71">
         <f>IFERROR(VLOOKUP(A92,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17468,7 +17618,7 @@
       </c>
       <c r="AS92" s="71">
         <f t="shared" si="5"/>
-        <v>1.3860148883375061</v>
+        <v>1.3360386300279146</v>
       </c>
     </row>
     <row r="93" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17580,18 +17730,20 @@
       <c r="AJ93" s="56">
         <v>23.533333333333331</v>
       </c>
-      <c r="AK93" s="56"/>
+      <c r="AK93" s="56">
+        <v>23.666666666666671</v>
+      </c>
       <c r="AL93" s="56"/>
       <c r="AM93" s="56"/>
       <c r="AN93" s="56"/>
       <c r="AO93" s="56"/>
       <c r="AP93" s="58">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ93" s="71">
         <f t="shared" si="4"/>
-        <v>23.617948717948714</v>
+        <v>23.619753086419749</v>
       </c>
       <c r="AR93" s="71">
         <f>IFERROR(VLOOKUP(A93,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17599,7 +17751,7 @@
       </c>
       <c r="AS93" s="71">
         <f t="shared" si="5"/>
-        <v>1.508460852079093</v>
+        <v>1.5102652205501279</v>
       </c>
     </row>
     <row r="94" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17711,18 +17863,20 @@
       <c r="AJ94" s="56">
         <v>16.350000000000001</v>
       </c>
-      <c r="AK94" s="56"/>
+      <c r="AK94" s="56">
+        <v>16.850000000000001</v>
+      </c>
       <c r="AL94" s="56"/>
       <c r="AM94" s="56"/>
       <c r="AN94" s="56"/>
       <c r="AO94" s="56"/>
       <c r="AP94" s="58">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ94" s="71">
         <f t="shared" si="4"/>
-        <v>17.275961538461541</v>
+        <v>17.26018518518519</v>
       </c>
       <c r="AR94" s="71">
         <f>IFERROR(VLOOKUP(A94,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17730,7 +17884,7 @@
       </c>
       <c r="AS94" s="71">
         <f t="shared" si="5"/>
-        <v>1.180734392526972</v>
+        <v>1.1649580392506209</v>
       </c>
     </row>
     <row r="95" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17842,18 +17996,20 @@
       <c r="AJ95" s="56">
         <v>14.25</v>
       </c>
-      <c r="AK95" s="56"/>
+      <c r="AK95" s="56">
+        <v>15.05</v>
+      </c>
       <c r="AL95" s="56"/>
       <c r="AM95" s="56"/>
       <c r="AN95" s="56"/>
       <c r="AO95" s="56"/>
       <c r="AP95" s="58">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ95" s="71">
         <f t="shared" si="4"/>
-        <v>14.673076923076923</v>
+        <v>14.687037037037037</v>
       </c>
       <c r="AR95" s="71">
         <f>IFERROR(VLOOKUP(A95,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17861,7 +18017,7 @@
       </c>
       <c r="AS95" s="71">
         <f t="shared" si="5"/>
-        <v>1.0402687869250631</v>
+        <v>1.0542289008851764</v>
       </c>
     </row>
     <row r="96" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18131,18 +18287,20 @@
       <c r="AJ98" s="56">
         <v>13</v>
       </c>
-      <c r="AK98" s="56"/>
+      <c r="AK98" s="56">
+        <v>12.45</v>
+      </c>
       <c r="AL98" s="56"/>
       <c r="AM98" s="56"/>
       <c r="AN98" s="56"/>
       <c r="AO98" s="56"/>
       <c r="AP98" s="58">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ98" s="71">
         <f t="shared" si="4"/>
-        <v>13.165384615384616</v>
+        <v>13.138888888888889</v>
       </c>
       <c r="AR98" s="71" t="str">
         <f>IFERROR(VLOOKUP(A98,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18258,18 +18416,20 @@
       <c r="AJ99" s="56">
         <v>13.96666666666667</v>
       </c>
-      <c r="AK99" s="56"/>
+      <c r="AK99" s="56">
+        <v>14.9</v>
+      </c>
       <c r="AL99" s="56"/>
       <c r="AM99" s="56"/>
       <c r="AN99" s="56"/>
       <c r="AO99" s="56"/>
       <c r="AP99" s="58">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ99" s="71">
         <f t="shared" si="4"/>
-        <v>14.459722222222226</v>
+        <v>14.477333333333336</v>
       </c>
       <c r="AR99" s="71" t="str">
         <f>IFERROR(VLOOKUP(A99,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18375,18 +18535,20 @@
       </c>
       <c r="AI100" s="56"/>
       <c r="AJ100" s="56"/>
-      <c r="AK100" s="56"/>
+      <c r="AK100" s="56">
+        <v>15.266666666666669</v>
+      </c>
       <c r="AL100" s="56"/>
       <c r="AM100" s="56"/>
       <c r="AN100" s="56"/>
       <c r="AO100" s="56"/>
       <c r="AP100" s="58">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ100" s="71">
         <f t="shared" si="4"/>
-        <v>16.245614035087719</v>
+        <v>16.196666666666665</v>
       </c>
       <c r="AR100" s="71">
         <f>IFERROR(VLOOKUP(A100,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18394,7 +18556,7 @@
       </c>
       <c r="AS100" s="71">
         <f t="shared" si="5"/>
-        <v>1.9362561289797284</v>
+        <v>1.8873087605586747</v>
       </c>
     </row>
     <row r="101" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18494,18 +18656,20 @@
         <v>12.2</v>
       </c>
       <c r="AJ101" s="56"/>
-      <c r="AK101" s="56"/>
+      <c r="AK101" s="56">
+        <v>13.5</v>
+      </c>
       <c r="AL101" s="56"/>
       <c r="AM101" s="56"/>
       <c r="AN101" s="56"/>
       <c r="AO101" s="56"/>
       <c r="AP101" s="58">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ101" s="71">
         <f t="shared" si="4"/>
-        <v>13.345000000000002</v>
+        <v>13.352380952380955</v>
       </c>
       <c r="AR101" s="71">
         <f>IFERROR(VLOOKUP(A101,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18513,7 +18677,7 @@
       </c>
       <c r="AS101" s="71">
         <f t="shared" si="5"/>
-        <v>1.0125963373887128</v>
+        <v>1.0199772897696651</v>
       </c>
     </row>
     <row r="102" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18619,18 +18783,20 @@
       <c r="AJ102" s="56">
         <v>13.06666666666667</v>
       </c>
-      <c r="AK102" s="56"/>
+      <c r="AK102" s="56">
+        <v>12.733333333333331</v>
+      </c>
       <c r="AL102" s="56"/>
       <c r="AM102" s="56"/>
       <c r="AN102" s="56"/>
       <c r="AO102" s="56"/>
       <c r="AP102" s="58">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ102" s="71">
         <f t="shared" si="4"/>
-        <v>13.037681159420293</v>
+        <v>13.025000000000004</v>
       </c>
       <c r="AR102" s="71">
         <f>IFERROR(VLOOKUP(A102,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18638,7 +18804,7 @@
       </c>
       <c r="AS102" s="71">
         <f t="shared" si="5"/>
-        <v>1.7906857900344022</v>
+        <v>1.7780046306141131</v>
       </c>
     </row>
     <row r="103" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18902,18 +19068,20 @@
       <c r="AJ105" s="56">
         <v>18.2</v>
       </c>
-      <c r="AK105" s="56"/>
+      <c r="AK105" s="56">
+        <v>19.600000000000001</v>
+      </c>
       <c r="AL105" s="56"/>
       <c r="AM105" s="56"/>
       <c r="AN105" s="56"/>
       <c r="AO105" s="56"/>
       <c r="AP105" s="58">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ105" s="71">
         <f t="shared" si="4"/>
-        <v>18.133333333333333</v>
+        <v>18.194444444444446</v>
       </c>
       <c r="AR105" s="71">
         <f>IFERROR(VLOOKUP(A105,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18921,7 +19089,7 @@
       </c>
       <c r="AS105" s="71">
         <f t="shared" si="5"/>
-        <v>1.0887958248570619</v>
+        <v>1.1499069359681755</v>
       </c>
     </row>
     <row r="106" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19088,26 +19256,28 @@
       <c r="AH107" s="56"/>
       <c r="AI107" s="56"/>
       <c r="AJ107" s="56"/>
-      <c r="AK107" s="56"/>
+      <c r="AK107" s="56">
+        <v>12.2</v>
+      </c>
       <c r="AL107" s="56"/>
       <c r="AM107" s="56"/>
       <c r="AN107" s="56"/>
       <c r="AO107" s="56"/>
       <c r="AP107" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ107" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ107" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>14.951111111111114</v>
       </c>
       <c r="AR107" s="71">
         <f>IFERROR(VLOOKUP(A107,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>13.42031660692947</v>
       </c>
-      <c r="AS107" s="71" t="str">
+      <c r="AS107" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1.5307945041816442</v>
       </c>
     </row>
     <row r="108" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19219,18 +19389,20 @@
       <c r="AJ108" s="56">
         <v>14.5</v>
       </c>
-      <c r="AK108" s="56"/>
+      <c r="AK108" s="56">
+        <v>13.25</v>
+      </c>
       <c r="AL108" s="56"/>
       <c r="AM108" s="56"/>
       <c r="AN108" s="56"/>
       <c r="AO108" s="56"/>
       <c r="AP108" s="58">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ108" s="71">
         <f t="shared" si="4"/>
-        <v>14.255769230769232</v>
+        <v>14.21851851851852</v>
       </c>
       <c r="AR108" s="71">
         <f>IFERROR(VLOOKUP(A108,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19238,7 +19410,7 @@
       </c>
       <c r="AS108" s="71">
         <f t="shared" si="5"/>
-        <v>2.6736316037421659E-2</v>
+        <v>-1.0514396213290311E-2</v>
       </c>
     </row>
     <row r="109" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19350,18 +19522,20 @@
       <c r="AJ109" s="56">
         <v>14.8</v>
       </c>
-      <c r="AK109" s="56"/>
+      <c r="AK109" s="56">
+        <v>14.2</v>
+      </c>
       <c r="AL109" s="56"/>
       <c r="AM109" s="56"/>
       <c r="AN109" s="56"/>
       <c r="AO109" s="56"/>
       <c r="AP109" s="58">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ109" s="71">
         <f t="shared" si="4"/>
-        <v>14.571153846153845</v>
+        <v>14.557407407407405</v>
       </c>
       <c r="AR109" s="71">
         <f>IFERROR(VLOOKUP(A109,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19369,7 +19543,7 @@
       </c>
       <c r="AS109" s="71">
         <f t="shared" si="5"/>
-        <v>0.85739075864605496</v>
+        <v>0.84364431989961552</v>
       </c>
     </row>
     <row r="110" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19481,18 +19655,20 @@
       <c r="AJ110" s="56">
         <v>17.533333333333331</v>
       </c>
-      <c r="AK110" s="56"/>
+      <c r="AK110" s="56">
+        <v>18.333333333333329</v>
+      </c>
       <c r="AL110" s="56"/>
       <c r="AM110" s="56"/>
       <c r="AN110" s="56"/>
       <c r="AO110" s="56"/>
       <c r="AP110" s="58">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ110" s="71">
         <f t="shared" si="4"/>
-        <v>17.497435897435892</v>
+        <v>17.528395061728389</v>
       </c>
       <c r="AR110" s="71">
         <f>IFERROR(VLOOKUP(A110,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19500,7 +19676,7 @@
       </c>
       <c r="AS110" s="71">
         <f t="shared" si="5"/>
-        <v>0.56247385896900326</v>
+        <v>0.59343302326150038</v>
       </c>
     </row>
     <row r="111" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19612,18 +19788,20 @@
       <c r="AJ111" s="56">
         <v>15.933333333333341</v>
       </c>
-      <c r="AK111" s="56"/>
+      <c r="AK111" s="56">
+        <v>15</v>
+      </c>
       <c r="AL111" s="56"/>
       <c r="AM111" s="56"/>
       <c r="AN111" s="56"/>
       <c r="AO111" s="56"/>
       <c r="AP111" s="58">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ111" s="71">
         <f t="shared" si="4"/>
-        <v>15.957692307692311</v>
+        <v>15.922222222222226</v>
       </c>
       <c r="AR111" s="71">
         <f>IFERROR(VLOOKUP(A111,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19631,7 +19809,7 @@
       </c>
       <c r="AS111" s="71">
         <f t="shared" si="5"/>
-        <v>0.45532878411912137</v>
+        <v>0.41985869864903691</v>
       </c>
     </row>
     <row r="112" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19743,18 +19921,20 @@
       <c r="AJ112" s="56">
         <v>17.533333333333331</v>
       </c>
-      <c r="AK112" s="56"/>
+      <c r="AK112" s="56">
+        <v>18.533333333333331</v>
+      </c>
       <c r="AL112" s="56"/>
       <c r="AM112" s="56"/>
       <c r="AN112" s="56"/>
       <c r="AO112" s="56"/>
       <c r="AP112" s="58">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ112" s="71">
         <f t="shared" si="4"/>
-        <v>17.805128205128202</v>
+        <v>17.832098765432097</v>
       </c>
       <c r="AR112" s="71">
         <f>IFERROR(VLOOKUP(A112,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19762,7 +19942,7 @@
       </c>
       <c r="AS112" s="71">
         <f t="shared" si="5"/>
-        <v>1.4254319440261227</v>
+        <v>1.4524025043300171</v>
       </c>
     </row>
     <row r="113" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19872,18 +20052,20 @@
       <c r="AJ113" s="56">
         <v>17.666666666666671</v>
       </c>
-      <c r="AK113" s="56"/>
+      <c r="AK113" s="56">
+        <v>18.399999999999999</v>
+      </c>
       <c r="AL113" s="56"/>
       <c r="AM113" s="56"/>
       <c r="AN113" s="56"/>
       <c r="AO113" s="56"/>
       <c r="AP113" s="58">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ113" s="71">
         <f t="shared" si="4"/>
-        <v>19.040000000000003</v>
+        <v>19.015384615384615</v>
       </c>
       <c r="AR113" s="71">
         <f>IFERROR(VLOOKUP(A113,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19891,7 +20073,7 @@
       </c>
       <c r="AS113" s="71">
         <f t="shared" si="5"/>
-        <v>0.91561253244347185</v>
+        <v>0.89099714782808448</v>
       </c>
     </row>
     <row r="114" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19969,14 +20151,16 @@
       <c r="AJ114" s="56">
         <v>22.8</v>
       </c>
-      <c r="AK114" s="56"/>
+      <c r="AK114" s="56">
+        <v>21.466666666666669</v>
+      </c>
       <c r="AL114" s="56"/>
       <c r="AM114" s="56"/>
       <c r="AN114" s="56"/>
       <c r="AO114" s="56"/>
       <c r="AP114" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ114" s="71" t="str">
         <f t="shared" si="4"/>
@@ -20098,20 +20282,22 @@
         <v>26.25</v>
       </c>
       <c r="AJ115" s="56">
-        <v>25.733333333333331</v>
-      </c>
-      <c r="AK115" s="56"/>
+        <v>25.9</v>
+      </c>
+      <c r="AK115" s="56">
+        <v>27.85</v>
+      </c>
       <c r="AL115" s="56"/>
       <c r="AM115" s="56"/>
       <c r="AN115" s="56"/>
       <c r="AO115" s="56"/>
       <c r="AP115" s="58">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ115" s="71">
         <f t="shared" si="4"/>
-        <v>26.198397435897434</v>
+        <v>26.265740740740739</v>
       </c>
       <c r="AR115" s="71">
         <f>IFERROR(VLOOKUP(A115,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20119,7 +20305,7 @@
       </c>
       <c r="AS115" s="71">
         <f t="shared" si="5"/>
-        <v>0.35391745814441222</v>
+        <v>0.42126076298771764</v>
       </c>
     </row>
     <row r="116" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20227,18 +20413,20 @@
       <c r="AJ116" s="56">
         <v>19.733333333333331</v>
       </c>
-      <c r="AK116" s="56"/>
+      <c r="AK116" s="56">
+        <v>19.8</v>
+      </c>
       <c r="AL116" s="56"/>
       <c r="AM116" s="56"/>
       <c r="AN116" s="56"/>
       <c r="AO116" s="56"/>
       <c r="AP116" s="58">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ116" s="71">
         <f t="shared" si="4"/>
-        <v>19.227777777777778</v>
+        <v>19.250666666666667</v>
       </c>
       <c r="AR116" s="71">
         <f>IFERROR(VLOOKUP(A116,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20246,7 +20434,7 @@
       </c>
       <c r="AS116" s="71">
         <f t="shared" si="5"/>
-        <v>0.83127261143695819</v>
+        <v>0.85416150032584781</v>
       </c>
     </row>
     <row r="117" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20358,18 +20546,20 @@
       <c r="AJ117" s="56">
         <v>24.8</v>
       </c>
-      <c r="AK117" s="56"/>
+      <c r="AK117" s="56">
+        <v>27.533333333333331</v>
+      </c>
       <c r="AL117" s="56"/>
       <c r="AM117" s="56"/>
       <c r="AN117" s="56"/>
       <c r="AO117" s="56"/>
       <c r="AP117" s="58">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ117" s="71">
         <f t="shared" si="4"/>
-        <v>26.174358974358977</v>
+        <v>26.224691358024693</v>
       </c>
       <c r="AR117" s="71">
         <f>IFERROR(VLOOKUP(A117,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20377,7 +20567,7 @@
       </c>
       <c r="AS117" s="71">
         <f t="shared" si="5"/>
-        <v>0.80551936862422835</v>
+        <v>0.85585175228994359</v>
       </c>
     </row>
     <row r="118" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20489,18 +20679,20 @@
       <c r="AJ118" s="56">
         <v>28.266666666666669</v>
       </c>
-      <c r="AK118" s="56"/>
+      <c r="AK118" s="56">
+        <v>29.93333333333333</v>
+      </c>
       <c r="AL118" s="56"/>
       <c r="AM118" s="56"/>
       <c r="AN118" s="56"/>
       <c r="AO118" s="56"/>
       <c r="AP118" s="58">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ118" s="71">
         <f t="shared" si="4"/>
-        <v>28.679487179487182</v>
+        <v>28.725925925925928</v>
       </c>
       <c r="AR118" s="71">
         <f>IFERROR(VLOOKUP(A118,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20508,7 +20700,7 @@
       </c>
       <c r="AS118" s="71">
         <f t="shared" si="5"/>
-        <v>2.9262076095947229</v>
+        <v>2.9726463560334686</v>
       </c>
     </row>
     <row r="119" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20620,18 +20812,20 @@
       <c r="AJ119" s="56">
         <v>23.6</v>
       </c>
-      <c r="AK119" s="56"/>
+      <c r="AK119" s="56">
+        <v>23.8</v>
+      </c>
       <c r="AL119" s="56"/>
       <c r="AM119" s="56"/>
       <c r="AN119" s="56"/>
       <c r="AO119" s="56"/>
       <c r="AP119" s="58">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ119" s="71">
         <f t="shared" si="4"/>
-        <v>23.617948717948721</v>
+        <v>23.624691358024691</v>
       </c>
       <c r="AR119" s="71">
         <f>IFERROR(VLOOKUP(A119,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20639,7 +20833,7 @@
       </c>
       <c r="AS119" s="71">
         <f t="shared" si="5"/>
-        <v>1.8895078577337117</v>
+        <v>1.8962504978096817</v>
       </c>
     </row>
     <row r="120" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20928,19 +21122,23 @@
       <c r="AI122" s="56">
         <v>12.8</v>
       </c>
-      <c r="AJ122" s="56"/>
-      <c r="AK122" s="56"/>
+      <c r="AJ122" s="56">
+        <v>10.6</v>
+      </c>
+      <c r="AK122" s="56">
+        <v>10.066666666666659</v>
+      </c>
       <c r="AL122" s="56"/>
       <c r="AM122" s="56"/>
       <c r="AN122" s="56"/>
       <c r="AO122" s="56"/>
       <c r="AP122" s="58">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AQ122" s="71">
         <f t="shared" si="4"/>
-        <v>12.198666666666666</v>
+        <v>12.060493827160494</v>
       </c>
       <c r="AR122" s="71">
         <f>IFERROR(VLOOKUP(A122,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20948,7 +21146,7 @@
       </c>
       <c r="AS122" s="71">
         <f t="shared" si="5"/>
-        <v>1.8959096706963869</v>
+        <v>1.7577368311902148</v>
       </c>
     </row>
     <row r="123" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21137,18 +21335,20 @@
       <c r="AJ124" s="56">
         <v>16.266666666666669</v>
       </c>
-      <c r="AK124" s="56"/>
+      <c r="AK124" s="56">
+        <v>16</v>
+      </c>
       <c r="AL124" s="56"/>
       <c r="AM124" s="56"/>
       <c r="AN124" s="56"/>
       <c r="AO124" s="56"/>
       <c r="AP124" s="58">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ124" s="71">
         <f t="shared" si="4"/>
-        <v>16.005333333333333</v>
+        <v>16.005128205128205</v>
       </c>
       <c r="AR124" s="71">
         <f>IFERROR(VLOOKUP(A124,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21156,7 +21356,7 @@
       </c>
       <c r="AS124" s="71">
         <f t="shared" si="5"/>
-        <v>0.95627437378982272</v>
+        <v>0.95606924558469508</v>
       </c>
     </row>
     <row r="125" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21333,18 +21533,20 @@
       <c r="AJ126" s="56">
         <v>11.66666666666667</v>
       </c>
-      <c r="AK126" s="56"/>
+      <c r="AK126" s="56">
+        <v>11.46666666666667</v>
+      </c>
       <c r="AL126" s="56"/>
       <c r="AM126" s="56"/>
       <c r="AN126" s="56"/>
       <c r="AO126" s="56"/>
       <c r="AP126" s="58">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ126" s="71">
         <f t="shared" si="4"/>
-        <v>11.89473684210526</v>
+        <v>11.873333333333331</v>
       </c>
       <c r="AR126" s="71">
         <f>IFERROR(VLOOKUP(A126,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21352,7 +21554,7 @@
       </c>
       <c r="AS126" s="71">
         <f t="shared" si="5"/>
-        <v>1.1822906260415209</v>
+        <v>1.160887117269592</v>
       </c>
     </row>
     <row r="127" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21829,19 +22031,23 @@
       <c r="AI131" s="56">
         <v>18.8</v>
       </c>
-      <c r="AJ131" s="56"/>
-      <c r="AK131" s="56"/>
+      <c r="AJ131" s="56">
+        <v>17.850000000000001</v>
+      </c>
+      <c r="AK131" s="56">
+        <v>17.55</v>
+      </c>
       <c r="AL131" s="56"/>
       <c r="AM131" s="56"/>
       <c r="AN131" s="56"/>
       <c r="AO131" s="56"/>
       <c r="AP131" s="58">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AQ131" s="71">
         <f t="shared" si="4"/>
-        <v>18.356000000000002</v>
+        <v>18.30740740740741</v>
       </c>
       <c r="AR131" s="71">
         <f>IFERROR(VLOOKUP(A131,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21849,7 +22055,7 @@
       </c>
       <c r="AS131" s="71">
         <f t="shared" si="5"/>
-        <v>1.5631030010960529</v>
+        <v>1.5145104085034617</v>
       </c>
     </row>
     <row r="132" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22040,18 +22246,20 @@
       <c r="AJ133" s="56">
         <v>13.2</v>
       </c>
-      <c r="AK133" s="56"/>
+      <c r="AK133" s="56">
+        <v>14.33333333333333</v>
+      </c>
       <c r="AL133" s="56"/>
       <c r="AM133" s="56"/>
       <c r="AN133" s="56"/>
       <c r="AO133" s="56"/>
       <c r="AP133" s="58">
         <f t="shared" ref="AP133:AP196" si="6">COUNTIF(K133:AO133,"&gt;0")</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ133" s="71">
         <f t="shared" ref="AQ133:AQ196" si="7">IF(AP133&gt;14,AVERAGE(K133:AO133),"")</f>
-        <v>13.870512820512818</v>
+        <v>13.887654320987652</v>
       </c>
       <c r="AR133" s="71">
         <f>IFERROR(VLOOKUP(A133,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22059,7 +22267,7 @@
       </c>
       <c r="AS133" s="71">
         <f t="shared" ref="AS133:AS196" si="8">IF(OR(AQ133="",AR133=""),"",IFERROR(AQ133-AR133,""))</f>
-        <v>1.2351730458589785</v>
+        <v>1.2523145463338121</v>
       </c>
     </row>
     <row r="134" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22171,18 +22379,20 @@
       <c r="AJ134" s="56">
         <v>16.466666666666669</v>
       </c>
-      <c r="AK134" s="56"/>
+      <c r="AK134" s="56">
+        <v>16.8</v>
+      </c>
       <c r="AL134" s="56"/>
       <c r="AM134" s="56"/>
       <c r="AN134" s="56"/>
       <c r="AO134" s="56"/>
       <c r="AP134" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ134" s="71">
         <f t="shared" si="7"/>
-        <v>17.833333333333332</v>
+        <v>17.795061728395062</v>
       </c>
       <c r="AR134" s="71">
         <f>IFERROR(VLOOKUP(A134,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22190,7 +22400,7 @@
       </c>
       <c r="AS134" s="71">
         <f t="shared" si="8"/>
-        <v>2.2511544909496628</v>
+        <v>2.2128828860113927</v>
       </c>
     </row>
     <row r="135" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22302,18 +22512,20 @@
       <c r="AJ135" s="56">
         <v>19.95</v>
       </c>
-      <c r="AK135" s="56"/>
+      <c r="AK135" s="56">
+        <v>18.850000000000001</v>
+      </c>
       <c r="AL135" s="56"/>
       <c r="AM135" s="56"/>
       <c r="AN135" s="56"/>
       <c r="AO135" s="56"/>
       <c r="AP135" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ135" s="71">
         <f t="shared" si="7"/>
-        <v>20.667307692307695</v>
+        <v>20.6</v>
       </c>
       <c r="AR135" s="71">
         <f>IFERROR(VLOOKUP(A135,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22321,7 +22533,7 @@
       </c>
       <c r="AS135" s="71">
         <f t="shared" si="8"/>
-        <v>1.9854270549025657</v>
+        <v>1.9181193625948723</v>
       </c>
     </row>
     <row r="136" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22643,18 +22855,20 @@
       <c r="AJ138" s="56">
         <v>21</v>
       </c>
-      <c r="AK138" s="56"/>
+      <c r="AK138" s="56">
+        <v>21.666666666666671</v>
+      </c>
       <c r="AL138" s="56"/>
       <c r="AM138" s="56"/>
       <c r="AN138" s="56"/>
       <c r="AO138" s="56"/>
       <c r="AP138" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ138" s="71">
         <f t="shared" si="7"/>
-        <v>22.176923076923078</v>
+        <v>22.158024691358023</v>
       </c>
       <c r="AR138" s="71">
         <f>IFERROR(VLOOKUP(A138,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22662,7 +22876,7 @@
       </c>
       <c r="AS138" s="71">
         <f t="shared" si="8"/>
-        <v>2.1667019795746789</v>
+        <v>2.1478035940096234</v>
       </c>
     </row>
     <row r="139" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22774,18 +22988,20 @@
       <c r="AJ139" s="56">
         <v>14.074999999999999</v>
       </c>
-      <c r="AK139" s="56"/>
+      <c r="AK139" s="56">
+        <v>14.3</v>
+      </c>
       <c r="AL139" s="56"/>
       <c r="AM139" s="56"/>
       <c r="AN139" s="56"/>
       <c r="AO139" s="56"/>
       <c r="AP139" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ139" s="71">
         <f t="shared" si="7"/>
-        <v>14.00480769230769</v>
+        <v>14.015740740740739</v>
       </c>
       <c r="AR139" s="71">
         <f>IFERROR(VLOOKUP(A139,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22793,7 +23009,7 @@
       </c>
       <c r="AS139" s="71">
         <f t="shared" si="8"/>
-        <v>1.1005899194736806</v>
+        <v>1.1115229679067298</v>
       </c>
     </row>
     <row r="140" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22905,18 +23121,20 @@
       <c r="AJ140" s="56">
         <v>15.35</v>
       </c>
-      <c r="AK140" s="56"/>
+      <c r="AK140" s="56">
+        <v>15.95</v>
+      </c>
       <c r="AL140" s="56"/>
       <c r="AM140" s="56"/>
       <c r="AN140" s="56"/>
       <c r="AO140" s="56"/>
       <c r="AP140" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ140" s="71">
         <f t="shared" si="7"/>
-        <v>16.401923076923079</v>
+        <v>16.385185185185186</v>
       </c>
       <c r="AR140" s="71">
         <f>IFERROR(VLOOKUP(A140,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22924,7 +23142,7 @@
       </c>
       <c r="AS140" s="71">
         <f t="shared" si="8"/>
-        <v>0.80757250515315882</v>
+        <v>0.79083461341526551</v>
       </c>
     </row>
     <row r="141" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23036,18 +23254,20 @@
       <c r="AJ141" s="56">
         <v>12.733333333333331</v>
       </c>
-      <c r="AK141" s="56"/>
+      <c r="AK141" s="56">
+        <v>13.6</v>
+      </c>
       <c r="AL141" s="56"/>
       <c r="AM141" s="56"/>
       <c r="AN141" s="56"/>
       <c r="AO141" s="56"/>
       <c r="AP141" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ141" s="71">
         <f t="shared" si="7"/>
-        <v>13.420512820512823</v>
+        <v>13.427160493827163</v>
       </c>
       <c r="AR141" s="71">
         <f>IFERROR(VLOOKUP(A141,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23055,7 +23275,7 @@
       </c>
       <c r="AS141" s="71">
         <f t="shared" si="8"/>
-        <v>1.4064834236747732</v>
+        <v>1.4131310969891135</v>
       </c>
     </row>
     <row r="142" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23165,18 +23385,20 @@
       <c r="AJ142" s="56">
         <v>10.55</v>
       </c>
-      <c r="AK142" s="56"/>
+      <c r="AK142" s="56">
+        <v>11.675000000000001</v>
+      </c>
       <c r="AL142" s="56"/>
       <c r="AM142" s="56"/>
       <c r="AN142" s="56"/>
       <c r="AO142" s="56"/>
       <c r="AP142" s="58">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ142" s="71">
         <f t="shared" si="7"/>
-        <v>11.599</v>
+        <v>11.601923076923079</v>
       </c>
       <c r="AR142" s="71">
         <f>IFERROR(VLOOKUP(A142,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23184,7 +23406,7 @@
       </c>
       <c r="AS142" s="71">
         <f t="shared" si="8"/>
-        <v>1.0700140235181994</v>
+        <v>1.072937100441278</v>
       </c>
     </row>
     <row r="143" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23296,18 +23518,20 @@
       <c r="AJ143" s="56">
         <v>28.06666666666667</v>
       </c>
-      <c r="AK143" s="56"/>
+      <c r="AK143" s="56">
+        <v>27.733333333333331</v>
+      </c>
       <c r="AL143" s="56"/>
       <c r="AM143" s="56"/>
       <c r="AN143" s="56"/>
       <c r="AO143" s="56"/>
       <c r="AP143" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ143" s="71">
         <f t="shared" si="7"/>
-        <v>27.674358974358974</v>
+        <v>27.676543209876542</v>
       </c>
       <c r="AR143" s="71">
         <f>IFERROR(VLOOKUP(A143,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23315,7 +23539,7 @@
       </c>
       <c r="AS143" s="71">
         <f t="shared" si="8"/>
-        <v>1.8124188821930929</v>
+        <v>1.8146031177106607</v>
       </c>
     </row>
     <row r="144" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23423,18 +23647,20 @@
       <c r="AJ144" s="56">
         <v>16.533333333333331</v>
       </c>
-      <c r="AK144" s="56"/>
+      <c r="AK144" s="56">
+        <v>14.6</v>
+      </c>
       <c r="AL144" s="56"/>
       <c r="AM144" s="56"/>
       <c r="AN144" s="56"/>
       <c r="AO144" s="56"/>
       <c r="AP144" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ144" s="71">
         <f t="shared" si="7"/>
-        <v>15.636111111111111</v>
+        <v>15.594666666666667</v>
       </c>
       <c r="AR144" s="71">
         <f>IFERROR(VLOOKUP(A144,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23442,7 +23668,7 @@
       </c>
       <c r="AS144" s="71">
         <f t="shared" si="8"/>
-        <v>-7.6774642803178139E-2</v>
+        <v>-0.11821908724762231</v>
       </c>
     </row>
     <row r="145" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23554,18 +23780,20 @@
       <c r="AJ145" s="56">
         <v>18.733333333333331</v>
       </c>
-      <c r="AK145" s="56"/>
+      <c r="AK145" s="56">
+        <v>20.2</v>
+      </c>
       <c r="AL145" s="56"/>
       <c r="AM145" s="56"/>
       <c r="AN145" s="56"/>
       <c r="AO145" s="56"/>
       <c r="AP145" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ145" s="71">
         <f t="shared" si="7"/>
-        <v>19.443589743589744</v>
+        <v>19.471604938271607</v>
       </c>
       <c r="AR145" s="71">
         <f>IFERROR(VLOOKUP(A145,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23573,7 +23801,7 @@
       </c>
       <c r="AS145" s="71">
         <f t="shared" si="8"/>
-        <v>0.40157320909162308</v>
+        <v>0.4295884037734865</v>
       </c>
     </row>
     <row r="146" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23685,18 +23913,20 @@
       <c r="AJ146" s="56">
         <v>29.2</v>
       </c>
-      <c r="AK146" s="56"/>
+      <c r="AK146" s="56">
+        <v>29.13333333333334</v>
+      </c>
       <c r="AL146" s="56"/>
       <c r="AM146" s="56"/>
       <c r="AN146" s="56"/>
       <c r="AO146" s="56"/>
       <c r="AP146" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ146" s="71">
         <f t="shared" si="7"/>
-        <v>29.897435897435894</v>
+        <v>29.869135802469131</v>
       </c>
       <c r="AR146" s="71">
         <f>IFERROR(VLOOKUP(A146,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23704,7 +23934,7 @@
       </c>
       <c r="AS146" s="71">
         <f t="shared" si="8"/>
-        <v>1.1402363596386635</v>
+        <v>1.1119362646719004</v>
       </c>
     </row>
     <row r="147" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23943,18 +24173,20 @@
       <c r="AJ148" s="56">
         <v>30.266666666666669</v>
       </c>
-      <c r="AK148" s="56"/>
+      <c r="AK148" s="56">
+        <v>29.8</v>
+      </c>
       <c r="AL148" s="56"/>
       <c r="AM148" s="56"/>
       <c r="AN148" s="56"/>
       <c r="AO148" s="56"/>
       <c r="AP148" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ148" s="71">
         <f t="shared" si="7"/>
-        <v>30.326388888888886</v>
+        <v>30.30533333333333</v>
       </c>
       <c r="AR148" s="71">
         <f>IFERROR(VLOOKUP(A148,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23962,7 +24194,7 @@
       </c>
       <c r="AS148" s="71">
         <f t="shared" si="8"/>
-        <v>1.6848576580341046</v>
+        <v>1.6638021024785488</v>
       </c>
     </row>
     <row r="149" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24074,18 +24306,20 @@
       <c r="AJ149" s="56">
         <v>22.333333333333329</v>
       </c>
-      <c r="AK149" s="56"/>
+      <c r="AK149" s="56">
+        <v>22.93333333333333</v>
+      </c>
       <c r="AL149" s="56"/>
       <c r="AM149" s="56"/>
       <c r="AN149" s="56"/>
       <c r="AO149" s="56"/>
       <c r="AP149" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ149" s="71">
         <f t="shared" si="7"/>
-        <v>23.523076923076925</v>
+        <v>23.501234567901232</v>
       </c>
       <c r="AR149" s="71">
         <f>IFERROR(VLOOKUP(A149,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24093,7 +24327,7 @@
       </c>
       <c r="AS149" s="71">
         <f t="shared" si="8"/>
-        <v>1.6470091501240738</v>
+        <v>1.625166794948381</v>
       </c>
     </row>
     <row r="150" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24277,19 +24511,23 @@
       </c>
       <c r="AH151" s="56"/>
       <c r="AI151" s="56"/>
-      <c r="AJ151" s="56"/>
-      <c r="AK151" s="56"/>
+      <c r="AJ151" s="56">
+        <v>22.43333333333333</v>
+      </c>
+      <c r="AK151" s="56">
+        <v>23</v>
+      </c>
       <c r="AL151" s="56"/>
       <c r="AM151" s="56"/>
       <c r="AN151" s="56"/>
       <c r="AO151" s="56"/>
       <c r="AP151" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AQ151" s="71">
         <f t="shared" si="7"/>
-        <v>23.279710144927535</v>
+        <v>23.234666666666662</v>
       </c>
       <c r="AR151" s="71">
         <f>IFERROR(VLOOKUP(A151,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24297,7 +24535,7 @@
       </c>
       <c r="AS151" s="71">
         <f t="shared" si="8"/>
-        <v>1.4671228663068945</v>
+        <v>1.4220793880460221</v>
       </c>
     </row>
     <row r="152" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24567,18 +24805,20 @@
       <c r="AJ154" s="56">
         <v>20.6</v>
       </c>
-      <c r="AK154" s="56"/>
+      <c r="AK154" s="56">
+        <v>20.100000000000001</v>
+      </c>
       <c r="AL154" s="56"/>
       <c r="AM154" s="56"/>
       <c r="AN154" s="56"/>
       <c r="AO154" s="56"/>
       <c r="AP154" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ154" s="71">
         <f t="shared" si="7"/>
-        <v>20.467307692307692</v>
+        <v>20.453703703703702</v>
       </c>
       <c r="AR154" s="71">
         <f>IFERROR(VLOOKUP(A154,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24586,7 +24826,7 @@
       </c>
       <c r="AS154" s="71">
         <f t="shared" si="8"/>
-        <v>0.95368693791275305</v>
+        <v>0.94008294930876346</v>
       </c>
     </row>
     <row r="155" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24698,18 +24938,20 @@
       <c r="AJ155" s="56">
         <v>27.86666666666666</v>
       </c>
-      <c r="AK155" s="56"/>
+      <c r="AK155" s="56">
+        <v>27.6</v>
+      </c>
       <c r="AL155" s="56"/>
       <c r="AM155" s="56"/>
       <c r="AN155" s="56"/>
       <c r="AO155" s="56"/>
       <c r="AP155" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ155" s="71">
         <f t="shared" si="7"/>
-        <v>28.876923076923074</v>
+        <v>28.829629629629629</v>
       </c>
       <c r="AR155" s="71">
         <f>IFERROR(VLOOKUP(A155,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24717,7 +24959,7 @@
       </c>
       <c r="AS155" s="71">
         <f t="shared" si="8"/>
-        <v>1.1541365160672754</v>
+        <v>1.1068430687738307</v>
       </c>
     </row>
     <row r="156" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24900,18 +25142,20 @@
       <c r="AJ157" s="56">
         <v>27.333333333333329</v>
       </c>
-      <c r="AK157" s="56"/>
+      <c r="AK157" s="56">
+        <v>28.4</v>
+      </c>
       <c r="AL157" s="56"/>
       <c r="AM157" s="56"/>
       <c r="AN157" s="56"/>
       <c r="AO157" s="56"/>
       <c r="AP157" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ157" s="71">
         <f t="shared" si="7"/>
-        <v>29.315151515151523</v>
+        <v>29.275362318840585</v>
       </c>
       <c r="AR157" s="71">
         <f>IFERROR(VLOOKUP(A157,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24919,7 +25163,7 @@
       </c>
       <c r="AS157" s="71">
         <f t="shared" si="8"/>
-        <v>1.7307240185421229</v>
+        <v>1.6909348222311849</v>
       </c>
     </row>
     <row r="158" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25025,18 +25269,20 @@
       <c r="AJ158" s="56">
         <v>29.333333333333329</v>
       </c>
-      <c r="AK158" s="56"/>
+      <c r="AK158" s="56">
+        <v>29.733333333333331</v>
+      </c>
       <c r="AL158" s="56"/>
       <c r="AM158" s="56"/>
       <c r="AN158" s="56"/>
       <c r="AO158" s="56"/>
       <c r="AP158" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ158" s="71">
         <f t="shared" si="7"/>
-        <v>30.00869565217392</v>
+        <v>29.997222222222231</v>
       </c>
       <c r="AR158" s="71">
         <f>IFERROR(VLOOKUP(A158,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25044,7 +25290,7 @@
       </c>
       <c r="AS158" s="71">
         <f t="shared" si="8"/>
-        <v>1.9902834850937197</v>
+        <v>1.9788100551420307</v>
       </c>
     </row>
     <row r="159" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25150,18 +25396,20 @@
       <c r="AJ159" s="56">
         <v>19.43333333333333</v>
       </c>
-      <c r="AK159" s="56"/>
+      <c r="AK159" s="56">
+        <v>19.666666666666671</v>
+      </c>
       <c r="AL159" s="56"/>
       <c r="AM159" s="56"/>
       <c r="AN159" s="56"/>
       <c r="AO159" s="56"/>
       <c r="AP159" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ159" s="71">
         <f t="shared" si="7"/>
-        <v>20.311594202898551</v>
+        <v>20.284722222222225</v>
       </c>
       <c r="AR159" s="71">
         <f>IFERROR(VLOOKUP(A159,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25169,7 +25417,7 @@
       </c>
       <c r="AS159" s="71">
         <f t="shared" si="8"/>
-        <v>1.3206570882081508</v>
+        <v>1.293785107531825</v>
       </c>
     </row>
     <row r="160" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25279,18 +25527,20 @@
       <c r="AJ160" s="56">
         <v>27.13333333333334</v>
       </c>
-      <c r="AK160" s="56"/>
+      <c r="AK160" s="56">
+        <v>26.86666666666666</v>
+      </c>
       <c r="AL160" s="56"/>
       <c r="AM160" s="56"/>
       <c r="AN160" s="56"/>
       <c r="AO160" s="56"/>
       <c r="AP160" s="58">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ160" s="71">
         <f t="shared" si="7"/>
-        <v>27.034666666666677</v>
+        <v>27.028205128205137</v>
       </c>
       <c r="AR160" s="71" t="str">
         <f>IFERROR(VLOOKUP(A160,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25385,7 +25635,9 @@
         <v>18.93333333333333</v>
       </c>
       <c r="AI161" s="56"/>
-      <c r="AJ161" s="56"/>
+      <c r="AJ161" s="56">
+        <v>18.533333333333331</v>
+      </c>
       <c r="AK161" s="56"/>
       <c r="AL161" s="56"/>
       <c r="AM161" s="56"/>
@@ -25393,19 +25645,19 @@
       <c r="AO161" s="56"/>
       <c r="AP161" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ161" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ161" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>19.137777777777782</v>
       </c>
       <c r="AR161" s="71">
         <f>IFERROR(VLOOKUP(A161,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>17.55988006564905</v>
       </c>
-      <c r="AS161" s="71" t="str">
+      <c r="AS161" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>1.5778977121287312</v>
       </c>
     </row>
     <row r="162" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25517,18 +25769,20 @@
       <c r="AJ162" s="56">
         <v>27.86666666666666</v>
       </c>
-      <c r="AK162" s="56"/>
+      <c r="AK162" s="56">
+        <v>28.13333333333334</v>
+      </c>
       <c r="AL162" s="56"/>
       <c r="AM162" s="56"/>
       <c r="AN162" s="56"/>
       <c r="AO162" s="56"/>
       <c r="AP162" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ162" s="71">
         <f t="shared" si="7"/>
-        <v>28.900000000000009</v>
+        <v>28.871604938271613</v>
       </c>
       <c r="AR162" s="71">
         <f>IFERROR(VLOOKUP(A162,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25536,7 +25790,7 @@
       </c>
       <c r="AS162" s="71">
         <f t="shared" si="8"/>
-        <v>0.3264626121257308</v>
+        <v>0.29806755039733446</v>
       </c>
     </row>
     <row r="163" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25648,18 +25902,20 @@
       <c r="AJ163" s="56">
         <v>21.333333333333329</v>
       </c>
-      <c r="AK163" s="56"/>
+      <c r="AK163" s="56">
+        <v>21.666666666666671</v>
+      </c>
       <c r="AL163" s="56"/>
       <c r="AM163" s="56"/>
       <c r="AN163" s="56"/>
       <c r="AO163" s="56"/>
       <c r="AP163" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ163" s="71">
         <f t="shared" si="7"/>
-        <v>21.402564102564103</v>
+        <v>21.412345679012347</v>
       </c>
       <c r="AR163" s="71">
         <f>IFERROR(VLOOKUP(A163,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25667,7 +25923,7 @@
       </c>
       <c r="AS163" s="71">
         <f t="shared" si="8"/>
-        <v>0.15314028696352366</v>
+        <v>0.16292186341176773</v>
       </c>
     </row>
     <row r="164" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25779,18 +26035,20 @@
       <c r="AJ164" s="56">
         <v>25.75</v>
       </c>
-      <c r="AK164" s="56"/>
+      <c r="AK164" s="56">
+        <v>24.85</v>
+      </c>
       <c r="AL164" s="56"/>
       <c r="AM164" s="56"/>
       <c r="AN164" s="56"/>
       <c r="AO164" s="56"/>
       <c r="AP164" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ164" s="71">
         <f t="shared" si="7"/>
-        <v>25.411538461538463</v>
+        <v>25.390740740740743</v>
       </c>
       <c r="AR164" s="71">
         <f>IFERROR(VLOOKUP(A164,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25798,7 +26056,7 @@
       </c>
       <c r="AS164" s="71">
         <f t="shared" si="8"/>
-        <v>1.6136108523783825</v>
+        <v>1.5928131315806624</v>
       </c>
     </row>
     <row r="165" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25985,18 +26243,20 @@
       <c r="AJ166" s="56">
         <v>12.66666666666667</v>
       </c>
-      <c r="AK166" s="56"/>
+      <c r="AK166" s="56">
+        <v>13.2</v>
+      </c>
       <c r="AL166" s="56"/>
       <c r="AM166" s="56"/>
       <c r="AN166" s="56"/>
       <c r="AO166" s="56"/>
       <c r="AP166" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ166" s="71">
         <f t="shared" si="7"/>
-        <v>14.77777777777778</v>
+        <v>14.71466666666667</v>
       </c>
       <c r="AR166" s="71">
         <f>IFERROR(VLOOKUP(A166,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26004,7 +26264,7 @@
       </c>
       <c r="AS166" s="71">
         <f t="shared" si="8"/>
-        <v>1.1793082437276396</v>
+        <v>1.116197132616529</v>
       </c>
     </row>
     <row r="167" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26112,18 +26372,20 @@
       <c r="AJ167" s="56">
         <v>20.533333333333331</v>
       </c>
-      <c r="AK167" s="56"/>
+      <c r="AK167" s="56">
+        <v>20.2</v>
+      </c>
       <c r="AL167" s="56"/>
       <c r="AM167" s="56"/>
       <c r="AN167" s="56"/>
       <c r="AO167" s="56"/>
       <c r="AP167" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ167" s="71">
         <f t="shared" si="7"/>
-        <v>20.669444444444448</v>
+        <v>20.65066666666667</v>
       </c>
       <c r="AR167" s="71">
         <f>IFERROR(VLOOKUP(A167,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26131,7 +26393,7 @@
       </c>
       <c r="AS167" s="71">
         <f t="shared" si="8"/>
-        <v>1.6338766348338076</v>
+        <v>1.6150988570560294</v>
       </c>
     </row>
     <row r="168" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26239,18 +26501,20 @@
       <c r="AJ168" s="56">
         <v>26.45</v>
       </c>
-      <c r="AK168" s="56"/>
+      <c r="AK168" s="56">
+        <v>27.2</v>
+      </c>
       <c r="AL168" s="56"/>
       <c r="AM168" s="56"/>
       <c r="AN168" s="56"/>
       <c r="AO168" s="56"/>
       <c r="AP168" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ168" s="71">
         <f t="shared" si="7"/>
-        <v>27.800000000000008</v>
+        <v>27.776000000000007</v>
       </c>
       <c r="AR168" s="71">
         <f>IFERROR(VLOOKUP(A168,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26258,7 +26522,7 @@
       </c>
       <c r="AS168" s="71">
         <f t="shared" si="8"/>
-        <v>1.7341355339334292</v>
+        <v>1.7101355339334283</v>
       </c>
     </row>
     <row r="169" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26370,18 +26634,20 @@
       <c r="AJ169" s="56">
         <v>9.3000000000000007</v>
       </c>
-      <c r="AK169" s="56"/>
+      <c r="AK169" s="56">
+        <v>9.1999999999999993</v>
+      </c>
       <c r="AL169" s="56"/>
       <c r="AM169" s="56"/>
       <c r="AN169" s="56"/>
       <c r="AO169" s="56"/>
       <c r="AP169" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ169" s="71">
         <f t="shared" si="7"/>
-        <v>8.9788461538461526</v>
+        <v>8.9870370370370356</v>
       </c>
       <c r="AR169" s="71">
         <f>IFERROR(VLOOKUP(A169,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26389,7 +26655,7 @@
       </c>
       <c r="AS169" s="71">
         <f t="shared" si="8"/>
-        <v>0.43672187249161531</v>
+        <v>0.44491275568249833</v>
       </c>
     </row>
     <row r="170" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26485,18 +26751,20 @@
       <c r="AJ170" s="56">
         <v>23.2</v>
       </c>
-      <c r="AK170" s="56"/>
+      <c r="AK170" s="56">
+        <v>25.733333333333331</v>
+      </c>
       <c r="AL170" s="56"/>
       <c r="AM170" s="56"/>
       <c r="AN170" s="56"/>
       <c r="AO170" s="56"/>
       <c r="AP170" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ170" s="71">
         <f t="shared" si="7"/>
-        <v>24.755555555555553</v>
+        <v>24.807017543859647</v>
       </c>
       <c r="AR170" s="71">
         <f>IFERROR(VLOOKUP(A170,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26504,7 +26772,7 @@
       </c>
       <c r="AS170" s="71">
         <f t="shared" si="8"/>
-        <v>0.6649316136930814</v>
+        <v>0.71639360199717572</v>
       </c>
     </row>
     <row r="171" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26614,18 +26882,20 @@
       <c r="AJ171" s="56">
         <v>19.8</v>
       </c>
-      <c r="AK171" s="56"/>
+      <c r="AK171" s="56">
+        <v>19.533333333333331</v>
+      </c>
       <c r="AL171" s="56"/>
       <c r="AM171" s="56"/>
       <c r="AN171" s="56"/>
       <c r="AO171" s="56"/>
       <c r="AP171" s="58">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ171" s="71">
         <f t="shared" si="7"/>
-        <v>20.754666666666665</v>
+        <v>20.707692307692305</v>
       </c>
       <c r="AR171" s="71">
         <f>IFERROR(VLOOKUP(A171,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26633,7 +26903,7 @@
       </c>
       <c r="AS171" s="71">
         <f t="shared" si="8"/>
-        <v>1.825740644414747</v>
+        <v>1.778766285440387</v>
       </c>
     </row>
     <row r="172" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26741,18 +27011,20 @@
       <c r="AJ172" s="56">
         <v>25.3</v>
       </c>
-      <c r="AK172" s="56"/>
+      <c r="AK172" s="56">
+        <v>25.95</v>
+      </c>
       <c r="AL172" s="56"/>
       <c r="AM172" s="56"/>
       <c r="AN172" s="56"/>
       <c r="AO172" s="56"/>
       <c r="AP172" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ172" s="71">
         <f t="shared" si="7"/>
-        <v>25.658333333333331</v>
+        <v>25.67</v>
       </c>
       <c r="AR172" s="71">
         <f>IFERROR(VLOOKUP(A172,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26760,7 +27032,7 @@
       </c>
       <c r="AS172" s="71">
         <f t="shared" si="8"/>
-        <v>1.2197049648214531</v>
+        <v>1.2313716314881233</v>
       </c>
     </row>
     <row r="173" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26872,18 +27144,20 @@
       <c r="AJ173" s="56">
         <v>25.1</v>
       </c>
-      <c r="AK173" s="56"/>
+      <c r="AK173" s="56">
+        <v>24.5</v>
+      </c>
       <c r="AL173" s="56"/>
       <c r="AM173" s="56"/>
       <c r="AN173" s="56"/>
       <c r="AO173" s="56"/>
       <c r="AP173" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ173" s="71">
         <f t="shared" si="7"/>
-        <v>25.123397435897441</v>
+        <v>25.100308641975314</v>
       </c>
       <c r="AR173" s="71">
         <f>IFERROR(VLOOKUP(A173,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26891,7 +27165,7 @@
       </c>
       <c r="AS173" s="71">
         <f t="shared" si="8"/>
-        <v>1.0689888337469107</v>
+        <v>1.0459000398247831</v>
       </c>
     </row>
     <row r="174" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27001,18 +27275,20 @@
       <c r="AJ174" s="56">
         <v>14.53333333333333</v>
       </c>
-      <c r="AK174" s="56"/>
+      <c r="AK174" s="56">
+        <v>15</v>
+      </c>
       <c r="AL174" s="56"/>
       <c r="AM174" s="56"/>
       <c r="AN174" s="56"/>
       <c r="AO174" s="56"/>
       <c r="AP174" s="58">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ174" s="71">
         <f t="shared" si="7"/>
-        <v>13.880000000000003</v>
+        <v>13.923076923076925</v>
       </c>
       <c r="AR174" s="71">
         <f>IFERROR(VLOOKUP(A174,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27020,7 +27296,7 @@
       </c>
       <c r="AS174" s="71">
         <f t="shared" si="8"/>
-        <v>1.8192481423281421</v>
+        <v>1.8623250654050647</v>
       </c>
     </row>
     <row r="175" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27401,18 +27677,20 @@
       <c r="AJ178" s="56">
         <v>24.6</v>
       </c>
-      <c r="AK178" s="56"/>
+      <c r="AK178" s="56">
+        <v>25.4</v>
+      </c>
       <c r="AL178" s="56"/>
       <c r="AM178" s="56"/>
       <c r="AN178" s="56"/>
       <c r="AO178" s="56"/>
       <c r="AP178" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ178" s="71">
         <f t="shared" si="7"/>
-        <v>25.12063492063492</v>
+        <v>25.133333333333329</v>
       </c>
       <c r="AR178" s="71">
         <f>IFERROR(VLOOKUP(A178,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27420,7 +27698,7 @@
       </c>
       <c r="AS178" s="71">
         <f t="shared" si="8"/>
-        <v>0.56835457375602871</v>
+        <v>0.58105298645443781</v>
       </c>
     </row>
     <row r="179" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27524,18 +27802,20 @@
       <c r="AJ179" s="56">
         <v>17.649999999999999</v>
       </c>
-      <c r="AK179" s="56"/>
+      <c r="AK179" s="56">
+        <v>17.5</v>
+      </c>
       <c r="AL179" s="56"/>
       <c r="AM179" s="56"/>
       <c r="AN179" s="56"/>
       <c r="AO179" s="56"/>
       <c r="AP179" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ179" s="71">
         <f t="shared" si="7"/>
-        <v>18.572727272727271</v>
+        <v>18.526086956521738</v>
       </c>
       <c r="AR179" s="71">
         <f>IFERROR(VLOOKUP(A179,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27543,7 +27823,7 @@
       </c>
       <c r="AS179" s="71">
         <f t="shared" si="8"/>
-        <v>0.98514358921061884</v>
+        <v>0.93850327300508596</v>
       </c>
     </row>
     <row r="180" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27734,18 +28014,20 @@
       <c r="AJ181" s="56">
         <v>31.8</v>
       </c>
-      <c r="AK181" s="56"/>
+      <c r="AK181" s="56">
+        <v>31.6</v>
+      </c>
       <c r="AL181" s="56"/>
       <c r="AM181" s="56"/>
       <c r="AN181" s="56"/>
       <c r="AO181" s="56"/>
       <c r="AP181" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ181" s="71">
         <f t="shared" si="7"/>
-        <v>30.941025641025639</v>
+        <v>30.965432098765429</v>
       </c>
       <c r="AR181" s="71">
         <f>IFERROR(VLOOKUP(A181,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27753,7 +28035,7 @@
       </c>
       <c r="AS181" s="71">
         <f t="shared" si="8"/>
-        <v>2.4077892534558281</v>
+        <v>2.4321957111956181</v>
       </c>
     </row>
     <row r="182" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28023,18 +28305,20 @@
       <c r="AJ184" s="56">
         <v>28.333333333333329</v>
       </c>
-      <c r="AK184" s="56"/>
+      <c r="AK184" s="56">
+        <v>27.8</v>
+      </c>
       <c r="AL184" s="56"/>
       <c r="AM184" s="56"/>
       <c r="AN184" s="56"/>
       <c r="AO184" s="56"/>
       <c r="AP184" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ184" s="71">
         <f t="shared" si="7"/>
-        <v>28.110256410256415</v>
+        <v>28.098765432098769</v>
       </c>
       <c r="AR184" s="71">
         <f>IFERROR(VLOOKUP(A184,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28042,7 +28326,7 @@
       </c>
       <c r="AS184" s="71">
         <f t="shared" si="8"/>
-        <v>1.4718851926394265</v>
+        <v>1.4603942144817808</v>
       </c>
     </row>
     <row r="185" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28146,18 +28430,20 @@
       <c r="AJ185" s="56">
         <v>29.266666666666669</v>
       </c>
-      <c r="AK185" s="56"/>
+      <c r="AK185" s="56">
+        <v>29</v>
+      </c>
       <c r="AL185" s="56"/>
       <c r="AM185" s="56"/>
       <c r="AN185" s="56"/>
       <c r="AO185" s="56"/>
       <c r="AP185" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ185" s="71">
         <f t="shared" si="7"/>
-        <v>28.930303030303026</v>
+        <v>28.93333333333333</v>
       </c>
       <c r="AR185" s="71">
         <f>IFERROR(VLOOKUP(A185,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28165,7 +28451,7 @@
       </c>
       <c r="AS185" s="71">
         <f t="shared" si="8"/>
-        <v>1.3216707452916552</v>
+        <v>1.324701048321959</v>
       </c>
     </row>
     <row r="186" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28435,18 +28721,20 @@
       <c r="AJ188" s="56">
         <v>16.2</v>
       </c>
-      <c r="AK188" s="56"/>
+      <c r="AK188" s="56">
+        <v>16.93333333333333</v>
+      </c>
       <c r="AL188" s="56"/>
       <c r="AM188" s="56"/>
       <c r="AN188" s="56"/>
       <c r="AO188" s="56"/>
       <c r="AP188" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ188" s="71">
         <f t="shared" si="7"/>
-        <v>17.31538461538462</v>
+        <v>17.30123456790124</v>
       </c>
       <c r="AR188" s="71">
         <f>IFERROR(VLOOKUP(A188,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28454,7 +28742,7 @@
       </c>
       <c r="AS188" s="71">
         <f t="shared" si="8"/>
-        <v>1.3197926258528891</v>
+        <v>1.3056425783695094</v>
       </c>
     </row>
     <row r="189" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28554,18 +28842,20 @@
       <c r="AJ189" s="56">
         <v>31.13333333333334</v>
       </c>
-      <c r="AK189" s="56"/>
+      <c r="AK189" s="56">
+        <v>32.133333333333333</v>
+      </c>
       <c r="AL189" s="56"/>
       <c r="AM189" s="56"/>
       <c r="AN189" s="56"/>
       <c r="AO189" s="56"/>
       <c r="AP189" s="58">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ189" s="71">
         <f t="shared" si="7"/>
-        <v>31.980000000000008</v>
+        <v>31.987301587301594</v>
       </c>
       <c r="AR189" s="71">
         <f>IFERROR(VLOOKUP(A189,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28573,7 +28863,7 @@
       </c>
       <c r="AS189" s="71">
         <f t="shared" si="8"/>
-        <v>2.1284156419472176</v>
+        <v>2.1357172292488045</v>
       </c>
     </row>
     <row r="190" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28685,18 +28975,20 @@
       <c r="AJ190" s="56">
         <v>28.6</v>
       </c>
-      <c r="AK190" s="56"/>
+      <c r="AK190" s="56">
+        <v>30.666666666666671</v>
+      </c>
       <c r="AL190" s="56"/>
       <c r="AM190" s="56"/>
       <c r="AN190" s="56"/>
       <c r="AO190" s="56"/>
       <c r="AP190" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ190" s="71">
         <f t="shared" si="7"/>
-        <v>30.533333333333335</v>
+        <v>30.53827160493827</v>
       </c>
       <c r="AR190" s="71">
         <f>IFERROR(VLOOKUP(A190,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28704,7 +28996,7 @@
       </c>
       <c r="AS190" s="71">
         <f t="shared" si="8"/>
-        <v>1.6168096718508664</v>
+        <v>1.6217479434558015</v>
       </c>
     </row>
     <row r="191" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28816,18 +29108,20 @@
       <c r="AJ191" s="56">
         <v>17.399999999999999</v>
       </c>
-      <c r="AK191" s="56"/>
+      <c r="AK191" s="56">
+        <v>17.2</v>
+      </c>
       <c r="AL191" s="56"/>
       <c r="AM191" s="56"/>
       <c r="AN191" s="56"/>
       <c r="AO191" s="56"/>
       <c r="AP191" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ191" s="71">
         <f t="shared" si="7"/>
-        <v>18.599999999999998</v>
+        <v>18.548148148148144</v>
       </c>
       <c r="AR191" s="71">
         <f>IFERROR(VLOOKUP(A191,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28835,7 +29129,7 @@
       </c>
       <c r="AS191" s="71">
         <f t="shared" si="8"/>
-        <v>1.2127809853393892</v>
+        <v>1.1609291334875351</v>
       </c>
     </row>
     <row r="192" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28947,18 +29241,20 @@
       <c r="AJ192" s="56">
         <v>26.2</v>
       </c>
-      <c r="AK192" s="56"/>
+      <c r="AK192" s="56">
+        <v>27.333333333333329</v>
+      </c>
       <c r="AL192" s="56"/>
       <c r="AM192" s="56"/>
       <c r="AN192" s="56"/>
       <c r="AO192" s="56"/>
       <c r="AP192" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ192" s="71">
         <f t="shared" si="7"/>
-        <v>26.151282051282063</v>
+        <v>26.195061728395075</v>
       </c>
       <c r="AR192" s="71">
         <f>IFERROR(VLOOKUP(A192,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28966,7 +29262,7 @@
       </c>
       <c r="AS192" s="71">
         <f t="shared" si="8"/>
-        <v>0.9067748704638916</v>
+        <v>0.95055454757690327</v>
       </c>
     </row>
     <row r="193" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29203,18 +29499,20 @@
       <c r="AJ194" s="56">
         <v>20.6</v>
       </c>
-      <c r="AK194" s="56"/>
+      <c r="AK194" s="56">
+        <v>20.399999999999999</v>
+      </c>
       <c r="AL194" s="56"/>
       <c r="AM194" s="56"/>
       <c r="AN194" s="56"/>
       <c r="AO194" s="56"/>
       <c r="AP194" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ194" s="71">
         <f t="shared" si="7"/>
-        <v>21.194871794871798</v>
+        <v>21.165432098765432</v>
       </c>
       <c r="AR194" s="71">
         <f>IFERROR(VLOOKUP(A194,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29222,7 +29520,7 @@
       </c>
       <c r="AS194" s="71">
         <f t="shared" si="8"/>
-        <v>-0.41279000218663242</v>
+        <v>-0.44222969829299785</v>
       </c>
     </row>
     <row r="195" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29334,18 +29632,20 @@
       <c r="AJ195" s="56">
         <v>26.266666666666669</v>
       </c>
-      <c r="AK195" s="56"/>
+      <c r="AK195" s="56">
+        <v>25.86666666666666</v>
+      </c>
       <c r="AL195" s="56"/>
       <c r="AM195" s="56"/>
       <c r="AN195" s="56"/>
       <c r="AO195" s="56"/>
       <c r="AP195" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ195" s="71">
         <f t="shared" si="7"/>
-        <v>27.638461538461538</v>
+        <v>27.572839506172841</v>
       </c>
       <c r="AR195" s="71">
         <f>IFERROR(VLOOKUP(A195,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29353,7 +29653,7 @@
       </c>
       <c r="AS195" s="71">
         <f t="shared" si="8"/>
-        <v>1.950973328751779</v>
+        <v>1.8853512964630816</v>
       </c>
     </row>
     <row r="196" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29465,18 +29765,20 @@
       <c r="AJ196" s="56">
         <v>21.2</v>
       </c>
-      <c r="AK196" s="56"/>
+      <c r="AK196" s="56">
+        <v>20.6</v>
+      </c>
       <c r="AL196" s="56"/>
       <c r="AM196" s="56"/>
       <c r="AN196" s="56"/>
       <c r="AO196" s="56"/>
       <c r="AP196" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ196" s="71">
         <f t="shared" si="7"/>
-        <v>22.125641025641031</v>
+        <v>22.069135802469141</v>
       </c>
       <c r="AR196" s="71">
         <f>IFERROR(VLOOKUP(A196,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29484,7 +29786,7 @@
       </c>
       <c r="AS196" s="71">
         <f t="shared" si="8"/>
-        <v>1.9018845541157603</v>
+        <v>1.8453793309438709</v>
       </c>
     </row>
     <row r="197" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29596,18 +29898,20 @@
       <c r="AJ197" s="56">
         <v>24.6</v>
       </c>
-      <c r="AK197" s="56"/>
+      <c r="AK197" s="56">
+        <v>26.6</v>
+      </c>
       <c r="AL197" s="56"/>
       <c r="AM197" s="56"/>
       <c r="AN197" s="56"/>
       <c r="AO197" s="56"/>
       <c r="AP197" s="58">
         <f t="shared" ref="AP197:AP260" si="9">COUNTIF(K197:AO197,"&gt;0")</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ197" s="71">
         <f t="shared" ref="AQ197:AQ260" si="10">IF(AP197&gt;14,AVERAGE(K197:AO197),"")</f>
-        <v>25.884615384615383</v>
+        <v>25.911111111111111</v>
       </c>
       <c r="AR197" s="71">
         <f>IFERROR(VLOOKUP(A197,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29615,7 +29919,7 @@
       </c>
       <c r="AS197" s="71">
         <f t="shared" ref="AS197:AS260" si="11">IF(OR(AQ197="",AR197=""),"",IFERROR(AQ197-AR197,""))</f>
-        <v>1.7572323834448547</v>
+        <v>1.7837281099405828</v>
       </c>
     </row>
     <row r="198" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29727,18 +30031,20 @@
       <c r="AJ198" s="56">
         <v>21.55</v>
       </c>
-      <c r="AK198" s="56"/>
+      <c r="AK198" s="56">
+        <v>20.95</v>
+      </c>
       <c r="AL198" s="56"/>
       <c r="AM198" s="56"/>
       <c r="AN198" s="56"/>
       <c r="AO198" s="56"/>
       <c r="AP198" s="58">
         <f t="shared" si="9"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ198" s="71">
         <f t="shared" si="10"/>
-        <v>21.621153846153842</v>
+        <v>21.596296296296291</v>
       </c>
       <c r="AR198" s="71" t="str">
         <f>IFERROR(VLOOKUP(A198,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29858,18 +30164,20 @@
       <c r="AJ199" s="56">
         <v>16.13333333333334</v>
       </c>
-      <c r="AK199" s="56"/>
+      <c r="AK199" s="56">
+        <v>16.13333333333334</v>
+      </c>
       <c r="AL199" s="56"/>
       <c r="AM199" s="56"/>
       <c r="AN199" s="56"/>
       <c r="AO199" s="56"/>
       <c r="AP199" s="58">
         <f t="shared" si="9"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ199" s="71">
         <f t="shared" si="10"/>
-        <v>16.592307692307692</v>
+        <v>16.575308641975308</v>
       </c>
       <c r="AR199" s="71">
         <f>IFERROR(VLOOKUP(A199,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29877,7 +30185,7 @@
       </c>
       <c r="AS199" s="71">
         <f t="shared" si="11"/>
-        <v>0.80464728611650216</v>
+        <v>0.78764823578411836</v>
       </c>
     </row>
     <row r="200" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29989,18 +30297,20 @@
       <c r="AJ200" s="56">
         <v>14.3</v>
       </c>
-      <c r="AK200" s="56"/>
+      <c r="AK200" s="56">
+        <v>14</v>
+      </c>
       <c r="AL200" s="56"/>
       <c r="AM200" s="56"/>
       <c r="AN200" s="56"/>
       <c r="AO200" s="56"/>
       <c r="AP200" s="58">
         <f t="shared" si="9"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ200" s="71">
         <f t="shared" si="10"/>
-        <v>14.667307692307693</v>
+        <v>14.642592592592594</v>
       </c>
       <c r="AR200" s="71">
         <f>IFERROR(VLOOKUP(A200,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -30008,7 +30318,7 @@
       </c>
       <c r="AS200" s="71">
         <f t="shared" si="11"/>
-        <v>1.3016952245240532</v>
+        <v>1.2769801248089543</v>
       </c>
     </row>
     <row r="201" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -30120,18 +30430,20 @@
       <c r="AJ201" s="56">
         <v>26.4</v>
       </c>
-      <c r="AK201" s="56"/>
+      <c r="AK201" s="56">
+        <v>26.35</v>
+      </c>
       <c r="AL201" s="56"/>
       <c r="AM201" s="56"/>
       <c r="AN201" s="56"/>
       <c r="AO201" s="56"/>
       <c r="AP201" s="58">
         <f t="shared" si="9"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ201" s="71">
         <f t="shared" si="10"/>
-        <v>27.111538461538455</v>
+        <v>27.083333333333329</v>
       </c>
       <c r="AR201" s="71">
         <f>IFERROR(VLOOKUP(A201,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -30139,7 +30451,7 @@
       </c>
       <c r="AS201" s="71">
         <f t="shared" si="11"/>
-        <v>1.5740091932076048</v>
+        <v>1.5458040650024785</v>
       </c>
     </row>
     <row r="202" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -30358,18 +30670,20 @@
       </c>
       <c r="AI203" s="56"/>
       <c r="AJ203" s="56"/>
-      <c r="AK203" s="56"/>
+      <c r="AK203" s="56">
+        <v>13.46666666666667</v>
+      </c>
       <c r="AL203" s="56"/>
       <c r="AM203" s="56"/>
       <c r="AN203" s="56"/>
       <c r="AO203" s="56"/>
       <c r="AP203" s="58">
         <f t="shared" si="9"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ203" s="71">
         <f t="shared" si="10"/>
-        <v>14.072727272727271</v>
+        <v>14.046376811594202</v>
       </c>
       <c r="AR203" s="71">
         <f>IFERROR(VLOOKUP(A203,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -30377,7 +30691,7 @@
       </c>
       <c r="AS203" s="71">
         <f t="shared" si="11"/>
-        <v>2.10185242224623</v>
+        <v>2.0755019611131615</v>
       </c>
     </row>
     <row r="204" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -30587,19 +30901,23 @@
       <c r="AI205" s="56">
         <v>14.5</v>
       </c>
-      <c r="AJ205" s="56"/>
-      <c r="AK205" s="56"/>
+      <c r="AJ205" s="56">
+        <v>16.25</v>
+      </c>
+      <c r="AK205" s="56">
+        <v>14.35</v>
+      </c>
       <c r="AL205" s="56"/>
       <c r="AM205" s="56"/>
       <c r="AN205" s="56"/>
       <c r="AO205" s="56"/>
       <c r="AP205" s="58">
         <f t="shared" si="9"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AQ205" s="71">
         <f t="shared" si="10"/>
-        <v>14.475999999999999</v>
+        <v>14.537037037037036</v>
       </c>
       <c r="AR205" s="71">
         <f>IFERROR(VLOOKUP(A205,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -30607,7 +30925,7 @@
       </c>
       <c r="AS205" s="71">
         <f t="shared" si="11"/>
-        <v>1.0611058831823286</v>
+        <v>1.1221429202193658</v>
       </c>
     </row>
     <row r="206" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -30822,18 +31140,20 @@
       </c>
       <c r="AI207" s="56"/>
       <c r="AJ207" s="56"/>
-      <c r="AK207" s="56"/>
+      <c r="AK207" s="56">
+        <v>14.53333333333333</v>
+      </c>
       <c r="AL207" s="56"/>
       <c r="AM207" s="56"/>
       <c r="AN207" s="56"/>
       <c r="AO207" s="56"/>
       <c r="AP207" s="58">
         <f t="shared" si="9"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ207" s="71">
         <f t="shared" si="10"/>
-        <v>14.270588235294115</v>
+        <v>14.285185185185181</v>
       </c>
       <c r="AR207" s="71">
         <f>IFERROR(VLOOKUP(A207,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -30841,7 +31161,7 @@
       </c>
       <c r="AS207" s="71">
         <f t="shared" si="11"/>
-        <v>0.70981243023139484</v>
+        <v>0.72440938012246114</v>
       </c>
     </row>
     <row r="208" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -30951,18 +31271,20 @@
       <c r="AJ208" s="56">
         <v>14.5</v>
       </c>
-      <c r="AK208" s="56"/>
+      <c r="AK208" s="56">
+        <v>14.6</v>
+      </c>
       <c r="AL208" s="56"/>
       <c r="AM208" s="56"/>
       <c r="AN208" s="56"/>
       <c r="AO208" s="56"/>
       <c r="AP208" s="58">
         <f t="shared" si="9"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ208" s="71">
         <f t="shared" si="10"/>
-        <v>14.163999999999996</v>
+        <v>14.180769230769227</v>
       </c>
       <c r="AR208" s="71" t="str">
         <f>IFERROR(VLOOKUP(A208,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -31079,19 +31401,23 @@
       <c r="AI209" s="56">
         <v>11.45</v>
       </c>
-      <c r="AJ209" s="56"/>
-      <c r="AK209" s="56"/>
+      <c r="AJ209" s="56">
+        <v>10.85</v>
+      </c>
+      <c r="AK209" s="56">
+        <v>11</v>
+      </c>
       <c r="AL209" s="56"/>
       <c r="AM209" s="56"/>
       <c r="AN209" s="56"/>
       <c r="AO209" s="56"/>
       <c r="AP209" s="58">
         <f t="shared" si="9"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AQ209" s="71">
         <f t="shared" si="10"/>
-        <v>11.096000000000002</v>
+        <v>11.083333333333336</v>
       </c>
       <c r="AR209" s="71" t="str">
         <f>IFERROR(VLOOKUP(A209,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -31204,19 +31530,23 @@
       </c>
       <c r="AH210" s="56"/>
       <c r="AI210" s="56"/>
-      <c r="AJ210" s="56"/>
-      <c r="AK210" s="56"/>
+      <c r="AJ210" s="56">
+        <v>16.850000000000001</v>
+      </c>
+      <c r="AK210" s="56">
+        <v>15.5</v>
+      </c>
       <c r="AL210" s="56"/>
       <c r="AM210" s="56"/>
       <c r="AN210" s="56"/>
       <c r="AO210" s="56"/>
       <c r="AP210" s="58">
         <f t="shared" si="9"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AQ210" s="71">
         <f t="shared" si="10"/>
-        <v>15.75</v>
+        <v>15.784000000000001</v>
       </c>
       <c r="AR210" s="71">
         <f>IFERROR(VLOOKUP(A210,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -31224,7 +31554,7 @@
       </c>
       <c r="AS210" s="71">
         <f t="shared" si="11"/>
-        <v>1.4203297947160696</v>
+        <v>1.4543297947160703</v>
       </c>
     </row>
     <row r="211" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -31332,18 +31662,20 @@
       </c>
       <c r="AI211" s="56"/>
       <c r="AJ211" s="56"/>
-      <c r="AK211" s="56"/>
+      <c r="AK211" s="56">
+        <v>8.4499999999999993</v>
+      </c>
       <c r="AL211" s="56"/>
       <c r="AM211" s="56"/>
       <c r="AN211" s="56"/>
       <c r="AO211" s="56"/>
       <c r="AP211" s="58">
         <f t="shared" si="9"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ211" s="71">
         <f t="shared" si="10"/>
-        <v>8.6291666666666647</v>
+        <v>8.6219999999999981</v>
       </c>
       <c r="AR211" s="71">
         <f>IFERROR(VLOOKUP(A211,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -31351,7 +31683,7 @@
       </c>
       <c r="AS211" s="71">
         <f t="shared" si="11"/>
-        <v>0.54903378497626498</v>
+        <v>0.54186711830959844</v>
       </c>
     </row>
     <row r="212" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -31463,18 +31795,20 @@
       <c r="AJ212" s="56">
         <v>27.05</v>
       </c>
-      <c r="AK212" s="56"/>
+      <c r="AK212" s="56">
+        <v>27.3</v>
+      </c>
       <c r="AL212" s="56"/>
       <c r="AM212" s="56"/>
       <c r="AN212" s="56"/>
       <c r="AO212" s="56"/>
       <c r="AP212" s="58">
         <f t="shared" si="9"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ212" s="71">
         <f t="shared" si="10"/>
-        <v>25.617307692307683</v>
+        <v>25.679629629629616</v>
       </c>
       <c r="AR212" s="71" t="str">
         <f>IFERROR(VLOOKUP(A212,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
